--- a/final/IQP_Database__Sharu_.xlsx
+++ b/final/IQP_Database__Sharu_.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cshar\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cshar\OneDrive\Desktop\IT Projects\Christianprojects\sourcesofthequran\final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A29FA0C-C92B-4132-9FAE-1222A75F01C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD16B79-E9A5-4D13-8777-E74448145264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Extra-Biblical Jewish" sheetId="1" r:id="rId1"/>
@@ -5232,9 +5232,6 @@
     </r>
   </si>
   <si>
-    <t>2:7–10; 12:11–14; 12:15</t>
-  </si>
-  <si>
     <t>12:7–10; 12:11–14; 12:15–18</t>
   </si>
   <si>
@@ -10497,6 +10494,9 @@
   <si>
     <t>15:16–18; 26:221–223; 37:6–10</t>
   </si>
+  <si>
+    <t>12:7–10; 12:11–14; 12:15</t>
+  </si>
 </sst>
 </file>
 
@@ -10506,7 +10506,7 @@
     <numFmt numFmtId="164" formatCode="yyyy&quot;/&quot;mm&quot;/&quot;dd"/>
     <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="54" x14ac:knownFonts="1">
+  <fonts count="55" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -10817,6 +10817,11 @@
       <sz val="10"/>
       <color rgb="FF34A853"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="18">
@@ -18841,14 +18846,14 @@
       <c r="F112" s="16" t="s">
         <v>462</v>
       </c>
-      <c r="G112" s="15" t="s">
+      <c r="G112" s="19" t="s">
+        <v>867</v>
+      </c>
+      <c r="H112" s="102" t="s">
         <v>465</v>
       </c>
-      <c r="H112" s="102" t="s">
+      <c r="M112" s="50" t="s">
         <v>466</v>
-      </c>
-      <c r="M112" s="50" t="s">
-        <v>467</v>
       </c>
       <c r="P112" s="12" t="s">
         <v>71</v>
@@ -18881,16 +18886,16 @@
         <v>55</v>
       </c>
       <c r="E113" s="12" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F113" s="16" t="s">
         <v>462</v>
       </c>
-      <c r="G113" s="15" t="s">
+      <c r="G113" s="19" t="s">
+        <v>867</v>
+      </c>
+      <c r="H113" s="102" t="s">
         <v>465</v>
-      </c>
-      <c r="H113" s="102" t="s">
-        <v>466</v>
       </c>
       <c r="P113" s="12" t="s">
         <v>102</v>
@@ -18921,16 +18926,16 @@
         <v>55</v>
       </c>
       <c r="E114" s="12" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F114" s="16" t="s">
         <v>462</v>
       </c>
-      <c r="G114" s="15" t="s">
+      <c r="G114" s="19" t="s">
+        <v>867</v>
+      </c>
+      <c r="H114" s="102" t="s">
         <v>465</v>
-      </c>
-      <c r="H114" s="102" t="s">
-        <v>466</v>
       </c>
       <c r="P114" s="12" t="s">
         <v>102</v>
@@ -18961,16 +18966,16 @@
         <v>55</v>
       </c>
       <c r="E115" s="12" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F115" s="16" t="s">
         <v>462</v>
       </c>
-      <c r="G115" s="15" t="s">
+      <c r="G115" s="19" t="s">
+        <v>867</v>
+      </c>
+      <c r="H115" s="102" t="s">
         <v>465</v>
-      </c>
-      <c r="H115" s="102" t="s">
-        <v>466</v>
       </c>
       <c r="P115" s="12" t="s">
         <v>102</v>
@@ -19001,16 +19006,16 @@
         <v>55</v>
       </c>
       <c r="E116" s="12" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F116" s="16" t="s">
         <v>462</v>
       </c>
-      <c r="G116" s="15" t="s">
+      <c r="G116" s="19" t="s">
+        <v>867</v>
+      </c>
+      <c r="H116" s="102" t="s">
         <v>465</v>
-      </c>
-      <c r="H116" s="102" t="s">
-        <v>466</v>
       </c>
       <c r="P116" s="12" t="s">
         <v>102</v>
@@ -19031,10 +19036,10 @@
     </row>
     <row r="117" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A117" s="104" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B117" s="104" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C117" s="105">
         <v>46185</v>
@@ -19043,16 +19048,16 @@
         <v>55</v>
       </c>
       <c r="E117" s="104" t="s">
+        <v>474</v>
+      </c>
+      <c r="F117" s="104" t="s">
+        <v>472</v>
+      </c>
+      <c r="G117" s="104" t="s">
         <v>475</v>
       </c>
-      <c r="F117" s="104" t="s">
-        <v>473</v>
-      </c>
-      <c r="G117" s="104" t="s">
+      <c r="H117" s="104" t="s">
         <v>476</v>
-      </c>
-      <c r="H117" s="104" t="s">
-        <v>477</v>
       </c>
       <c r="I117" s="104"/>
       <c r="J117" s="104" t="s">
@@ -19063,7 +19068,7 @@
       <c r="M117" s="104"/>
       <c r="N117" s="104"/>
       <c r="O117" s="107" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="P117" s="104" t="s">
         <v>71</v>
@@ -19094,7 +19099,7 @@
       </c>
       <c r="AK117" s="104"/>
       <c r="AL117" s="104" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AM117" s="104"/>
       <c r="AN117" s="104"/>
@@ -19138,10 +19143,10 @@
     </row>
     <row r="118" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A118" s="12" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B118" s="12" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C118" s="13">
         <v>46185</v>
@@ -19150,16 +19155,16 @@
         <v>55</v>
       </c>
       <c r="E118" s="12" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F118" s="12" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="G118" s="12" t="s">
+        <v>475</v>
+      </c>
+      <c r="H118" s="12" t="s">
         <v>476</v>
-      </c>
-      <c r="H118" s="12" t="s">
-        <v>477</v>
       </c>
       <c r="N118" s="12" t="s">
         <v>313</v>
@@ -19171,7 +19176,7 @@
         <v>57</v>
       </c>
       <c r="AF118" s="72" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AI118" s="31" t="s">
         <v>275</v>
@@ -19185,10 +19190,10 @@
     </row>
     <row r="119" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A119" s="12" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B119" s="12" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C119" s="13">
         <v>46185</v>
@@ -19197,28 +19202,28 @@
         <v>55</v>
       </c>
       <c r="E119" s="12" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F119" s="12" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="G119" s="12" t="s">
+        <v>475</v>
+      </c>
+      <c r="H119" s="12" t="s">
         <v>476</v>
-      </c>
-      <c r="H119" s="12" t="s">
-        <v>477</v>
       </c>
       <c r="J119" s="12" t="s">
         <v>170</v>
       </c>
       <c r="L119" s="12" t="s">
+        <v>484</v>
+      </c>
+      <c r="M119" s="50" t="s">
         <v>485</v>
       </c>
-      <c r="M119" s="50" t="s">
-        <v>486</v>
-      </c>
       <c r="O119" s="109" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="P119" s="12" t="s">
         <v>71</v>
@@ -19227,10 +19232,10 @@
         <v>73</v>
       </c>
       <c r="AJ119" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="AL119" s="12" t="s">
         <v>487</v>
-      </c>
-      <c r="AL119" s="12" t="s">
-        <v>488</v>
       </c>
       <c r="AR119" s="14"/>
       <c r="AS119" s="14"/>
@@ -19241,10 +19246,10 @@
     </row>
     <row r="120" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A120" s="12" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B120" s="12" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C120" s="13">
         <v>46185</v>
@@ -19253,26 +19258,26 @@
         <v>55</v>
       </c>
       <c r="E120" s="12" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F120" s="12" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="G120" s="12" t="s">
+        <v>475</v>
+      </c>
+      <c r="H120" s="12" t="s">
         <v>476</v>
-      </c>
-      <c r="H120" s="12" t="s">
-        <v>477</v>
       </c>
       <c r="J120" s="12" t="s">
         <v>170</v>
       </c>
       <c r="M120" s="50" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="N120" s="12"/>
       <c r="O120" s="109" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="P120" s="12" t="s">
         <v>71</v>
@@ -19281,7 +19286,7 @@
         <v>275</v>
       </c>
       <c r="AL120" s="12" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AR120" s="14"/>
       <c r="AS120" s="14"/>
@@ -19292,10 +19297,10 @@
     </row>
     <row r="121" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A121" s="12" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B121" s="110" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C121" s="13">
         <v>46185</v>
@@ -19304,25 +19309,25 @@
         <v>55</v>
       </c>
       <c r="E121" s="12" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F121" s="12" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="G121" s="12" t="s">
+        <v>475</v>
+      </c>
+      <c r="H121" s="12" t="s">
         <v>476</v>
-      </c>
-      <c r="H121" s="12" t="s">
-        <v>477</v>
       </c>
       <c r="J121" s="12" t="s">
         <v>170</v>
       </c>
       <c r="M121" s="50" t="s">
+        <v>494</v>
+      </c>
+      <c r="O121" s="109" t="s">
         <v>495</v>
-      </c>
-      <c r="O121" s="109" t="s">
-        <v>496</v>
       </c>
       <c r="P121" s="12" t="s">
         <v>71</v>
@@ -19345,10 +19350,10 @@
     </row>
     <row r="122" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A122" s="12" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B122" s="111" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C122" s="13">
         <v>46185</v>
@@ -19357,22 +19362,22 @@
         <v>55</v>
       </c>
       <c r="E122" s="12" t="s">
+        <v>497</v>
+      </c>
+      <c r="F122" s="12" t="s">
+        <v>472</v>
+      </c>
+      <c r="G122" s="12" t="s">
+        <v>475</v>
+      </c>
+      <c r="H122" s="12" t="s">
+        <v>476</v>
+      </c>
+      <c r="J122" s="19" t="s">
         <v>498</v>
       </c>
-      <c r="F122" s="12" t="s">
-        <v>473</v>
-      </c>
-      <c r="G122" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="H122" s="12" t="s">
-        <v>477</v>
-      </c>
-      <c r="J122" s="19" t="s">
+      <c r="N122" s="112" t="s">
         <v>499</v>
-      </c>
-      <c r="N122" s="112" t="s">
-        <v>500</v>
       </c>
       <c r="P122" s="12" t="s">
         <v>56</v>
@@ -19384,7 +19389,7 @@
         <v>275</v>
       </c>
       <c r="AJ122" s="12" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AR122" s="14"/>
       <c r="AS122" s="14"/>
@@ -19395,7 +19400,7 @@
     </row>
     <row r="123" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A123" s="12" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B123" s="14"/>
       <c r="C123" s="13">
@@ -19405,16 +19410,16 @@
         <v>55</v>
       </c>
       <c r="E123" s="12" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="F123" s="12" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="G123" s="12" t="s">
+        <v>475</v>
+      </c>
+      <c r="H123" s="12" t="s">
         <v>476</v>
-      </c>
-      <c r="H123" s="12" t="s">
-        <v>477</v>
       </c>
       <c r="P123" s="12" t="s">
         <v>102</v>
@@ -19430,10 +19435,10 @@
       </c>
       <c r="AP123" s="14"/>
       <c r="AR123" t="s">
+        <v>502</v>
+      </c>
+      <c r="AS123" t="s">
         <v>503</v>
-      </c>
-      <c r="AS123" t="s">
-        <v>504</v>
       </c>
       <c r="BA123" s="19" t="s">
         <v>62</v>
@@ -19442,7 +19447,7 @@
     </row>
     <row r="124" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A124" s="12" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B124" s="14"/>
       <c r="C124" s="13">
@@ -19452,16 +19457,16 @@
         <v>55</v>
       </c>
       <c r="E124" s="12" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="F124" s="12" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="G124" s="12" t="s">
+        <v>475</v>
+      </c>
+      <c r="H124" s="12" t="s">
         <v>476</v>
-      </c>
-      <c r="H124" s="12" t="s">
-        <v>477</v>
       </c>
       <c r="P124" s="12" t="s">
         <v>102</v>
@@ -19477,10 +19482,10 @@
       </c>
       <c r="AP124" s="14"/>
       <c r="AR124" t="s">
+        <v>505</v>
+      </c>
+      <c r="AS124" t="s">
         <v>506</v>
-      </c>
-      <c r="AS124" t="s">
-        <v>507</v>
       </c>
       <c r="BA124" s="19" t="s">
         <v>62</v>
@@ -19489,7 +19494,7 @@
     </row>
     <row r="125" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A125" s="12" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B125" s="14"/>
       <c r="C125" s="13">
@@ -19499,16 +19504,16 @@
         <v>55</v>
       </c>
       <c r="E125" s="12" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F125" s="12" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="G125" s="12" t="s">
+        <v>475</v>
+      </c>
+      <c r="H125" s="12" t="s">
         <v>476</v>
-      </c>
-      <c r="H125" s="12" t="s">
-        <v>477</v>
       </c>
       <c r="P125" s="12" t="s">
         <v>102</v>
@@ -19524,10 +19529,10 @@
       </c>
       <c r="AP125" s="14"/>
       <c r="AR125" t="s">
+        <v>508</v>
+      </c>
+      <c r="AS125" t="s">
         <v>509</v>
-      </c>
-      <c r="AS125" t="s">
-        <v>510</v>
       </c>
       <c r="BA125" s="19" t="s">
         <v>62</v>
@@ -19536,7 +19541,7 @@
     </row>
     <row r="126" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A126" s="12" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B126" s="14"/>
       <c r="C126" s="13">
@@ -19546,16 +19551,16 @@
         <v>55</v>
       </c>
       <c r="E126" s="12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F126" s="12" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="G126" s="12" t="s">
+        <v>475</v>
+      </c>
+      <c r="H126" s="12" t="s">
         <v>476</v>
-      </c>
-      <c r="H126" s="12" t="s">
-        <v>477</v>
       </c>
       <c r="P126" s="12" t="s">
         <v>102</v>
@@ -19571,7 +19576,7 @@
       </c>
       <c r="AP126" s="14"/>
       <c r="AR126" s="16" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="BA126" s="19" t="s">
         <v>62</v>
@@ -19580,7 +19585,7 @@
     </row>
     <row r="127" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A127" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B127" s="16"/>
       <c r="C127" s="24">
@@ -19590,13 +19595,13 @@
         <v>55</v>
       </c>
       <c r="E127" s="12" t="s">
+        <v>513</v>
+      </c>
+      <c r="F127" s="12" t="s">
+        <v>512</v>
+      </c>
+      <c r="G127" s="15" t="s">
         <v>514</v>
-      </c>
-      <c r="F127" s="12" t="s">
-        <v>513</v>
-      </c>
-      <c r="G127" s="15" t="s">
-        <v>515</v>
       </c>
       <c r="H127" s="113"/>
       <c r="I127" s="16"/>
@@ -19625,10 +19630,10 @@
     </row>
     <row r="128" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A128" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B128" s="57" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C128" s="24">
         <v>46121</v>
@@ -19637,26 +19642,26 @@
         <v>55</v>
       </c>
       <c r="E128" s="12" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F128" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="G128" s="15" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H128" s="113"/>
       <c r="I128" s="16"/>
       <c r="K128" s="12"/>
       <c r="L128" s="12"/>
       <c r="M128" s="40" t="s">
+        <v>517</v>
+      </c>
+      <c r="N128" s="41" t="s">
         <v>518</v>
       </c>
-      <c r="N128" s="41" t="s">
+      <c r="O128" s="42" t="s">
         <v>519</v>
-      </c>
-      <c r="O128" s="42" t="s">
-        <v>520</v>
       </c>
       <c r="P128" s="15" t="s">
         <v>71</v>
@@ -19697,7 +19702,7 @@
     </row>
     <row r="129" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A129" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B129" s="14"/>
       <c r="C129" s="24">
@@ -19707,20 +19712,20 @@
         <v>55</v>
       </c>
       <c r="E129" s="12" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F129" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="G129" s="15" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H129" s="100"/>
       <c r="BC129" s="19"/>
     </row>
     <row r="130" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A130" s="12" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C130" s="13">
         <v>46185</v>
@@ -19729,16 +19734,16 @@
         <v>55</v>
       </c>
       <c r="E130" s="12" t="s">
+        <v>523</v>
+      </c>
+      <c r="F130" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="G130" s="93" t="s">
         <v>524</v>
       </c>
-      <c r="F130" s="12" t="s">
-        <v>523</v>
-      </c>
-      <c r="G130" s="93" t="s">
+      <c r="H130" s="114" t="s">
         <v>525</v>
-      </c>
-      <c r="H130" s="114" t="s">
-        <v>526</v>
       </c>
       <c r="AR130" s="14"/>
       <c r="AS130" s="14"/>
@@ -19749,7 +19754,7 @@
     </row>
     <row r="131" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A131" s="12" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C131" s="13">
         <v>46185</v>
@@ -19758,16 +19763,16 @@
         <v>55</v>
       </c>
       <c r="E131" s="12" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="F131" s="12" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="G131" s="93" t="s">
+        <v>524</v>
+      </c>
+      <c r="H131" s="114" t="s">
         <v>525</v>
-      </c>
-      <c r="H131" s="114" t="s">
-        <v>526</v>
       </c>
       <c r="AR131" s="14"/>
       <c r="AS131" s="14"/>
@@ -19778,10 +19783,10 @@
     </row>
     <row r="132" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A132" s="12" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B132" s="57" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C132" s="13">
         <v>46186</v>
@@ -19790,26 +19795,26 @@
         <v>55</v>
       </c>
       <c r="E132" s="12" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F132" s="12" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="G132" s="93" t="s">
+        <v>524</v>
+      </c>
+      <c r="H132" s="114" t="s">
         <v>525</v>
-      </c>
-      <c r="H132" s="114" t="s">
-        <v>526</v>
       </c>
       <c r="I132" s="16"/>
       <c r="K132" s="12"/>
       <c r="L132" s="12"/>
       <c r="M132" s="12"/>
       <c r="N132" s="41" t="s">
+        <v>529</v>
+      </c>
+      <c r="O132" t="s">
         <v>530</v>
-      </c>
-      <c r="O132" t="s">
-        <v>531</v>
       </c>
       <c r="P132" s="15" t="s">
         <v>71</v>
@@ -19819,7 +19824,7 @@
       </c>
       <c r="R132" s="16"/>
       <c r="S132" s="115" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="T132" s="15"/>
       <c r="X132" s="16" t="s">
@@ -19851,7 +19856,7 @@
     </row>
     <row r="133" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A133" s="12" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B133" s="14"/>
       <c r="C133" s="13">
@@ -19861,16 +19866,16 @@
         <v>55</v>
       </c>
       <c r="E133" s="12" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F133" s="12" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="G133" s="93" t="s">
+        <v>524</v>
+      </c>
+      <c r="H133" s="114" t="s">
         <v>525</v>
-      </c>
-      <c r="H133" s="114" t="s">
-        <v>526</v>
       </c>
       <c r="AH133" s="16" t="s">
         <v>104</v>
@@ -19880,7 +19885,7 @@
       </c>
       <c r="AP133" s="14"/>
       <c r="AR133" s="12" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AS133" s="100"/>
       <c r="BA133" s="12" t="s">
@@ -19890,10 +19895,10 @@
     </row>
     <row r="134" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A134" s="12" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B134" s="100" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C134" s="65">
         <v>46284</v>
@@ -19902,23 +19907,23 @@
         <v>55</v>
       </c>
       <c r="E134" s="12" t="s">
+        <v>535</v>
+      </c>
+      <c r="F134" s="12" t="s">
         <v>536</v>
       </c>
-      <c r="F134" s="12" t="s">
-        <v>537</v>
-      </c>
       <c r="G134" s="93" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H134" s="100"/>
       <c r="J134" s="19" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="Q134" s="12" t="s">
         <v>57</v>
       </c>
       <c r="S134" s="100" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AR134" s="14"/>
       <c r="AS134" s="14"/>
@@ -19929,10 +19934,10 @@
     </row>
     <row r="135" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A135" s="12" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B135" s="19" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C135" s="65">
         <v>46284</v>
@@ -19941,13 +19946,13 @@
         <v>55</v>
       </c>
       <c r="E135" s="12" t="s">
+        <v>535</v>
+      </c>
+      <c r="F135" s="12" t="s">
         <v>536</v>
       </c>
-      <c r="F135" s="12" t="s">
-        <v>537</v>
-      </c>
       <c r="G135" s="93" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H135" s="100"/>
       <c r="J135" s="12" t="s">
@@ -19957,7 +19962,7 @@
         <v>57</v>
       </c>
       <c r="S135" s="100" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AR135" s="14"/>
       <c r="AS135" s="14"/>
@@ -19968,10 +19973,10 @@
     </row>
     <row r="136" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A136" s="12" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B136" s="100" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C136" s="65">
         <v>46284</v>
@@ -19980,13 +19985,13 @@
         <v>55</v>
       </c>
       <c r="E136" s="12" t="s">
+        <v>535</v>
+      </c>
+      <c r="F136" s="12" t="s">
         <v>536</v>
       </c>
-      <c r="F136" s="12" t="s">
-        <v>537</v>
-      </c>
       <c r="G136" s="93" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H136" s="100"/>
       <c r="J136" s="12" t="s">
@@ -20007,7 +20012,7 @@
     </row>
     <row r="137" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A137" s="12" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B137" s="14"/>
       <c r="C137" s="65">
@@ -20017,13 +20022,13 @@
         <v>55</v>
       </c>
       <c r="E137" s="12" t="s">
+        <v>535</v>
+      </c>
+      <c r="F137" s="12" t="s">
         <v>536</v>
       </c>
-      <c r="F137" s="12" t="s">
-        <v>537</v>
-      </c>
       <c r="G137" s="93" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H137" s="100"/>
       <c r="J137" s="12" t="s">
@@ -20040,7 +20045,7 @@
       </c>
       <c r="AP137" s="14"/>
       <c r="AR137" s="100" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="BA137" s="19" t="s">
         <v>62</v>
@@ -20049,7 +20054,7 @@
     </row>
     <row r="138" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A138" s="19" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B138" s="15" t="s">
         <v>161</v>
@@ -20061,16 +20066,16 @@
         <v>55</v>
       </c>
       <c r="E138" s="12" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F138" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="G138" s="84" t="s">
         <v>548</v>
       </c>
-      <c r="G138" s="84" t="s">
-        <v>549</v>
-      </c>
       <c r="H138" s="16" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="I138" s="16" t="s">
         <v>162</v>
@@ -20081,13 +20086,13 @@
       <c r="K138" s="16"/>
       <c r="L138" s="16"/>
       <c r="M138" s="116" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="N138" s="16" t="s">
         <v>164</v>
       </c>
       <c r="O138" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="P138" s="15" t="s">
         <v>71</v>
@@ -20097,7 +20102,7 @@
       </c>
       <c r="R138" s="16"/>
       <c r="S138" s="115" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="T138" s="16"/>
       <c r="U138" s="16"/>
@@ -20127,7 +20132,7 @@
       <c r="AK138" s="16"/>
       <c r="AL138" s="16"/>
       <c r="AM138" s="16" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AN138" s="16"/>
       <c r="AO138" s="16"/>
@@ -20138,7 +20143,7 @@
       <c r="AR138" s="82"/>
       <c r="AS138" s="82"/>
       <c r="AT138" s="16" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AU138" s="16"/>
       <c r="AV138" s="16"/>
@@ -20155,10 +20160,10 @@
     </row>
     <row r="139" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A139" s="19" t="s">
+        <v>554</v>
+      </c>
+      <c r="B139" s="16" t="s">
         <v>555</v>
-      </c>
-      <c r="B139" s="16" t="s">
-        <v>556</v>
       </c>
       <c r="C139" s="65">
         <v>46185</v>
@@ -20167,29 +20172,29 @@
         <v>55</v>
       </c>
       <c r="E139" s="12" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F139" s="19" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="G139" s="84" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H139" s="16" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="I139" s="16"/>
       <c r="J139" s="16"/>
       <c r="K139" s="16"/>
       <c r="L139" s="16"/>
       <c r="M139" s="58" t="s">
+        <v>557</v>
+      </c>
+      <c r="N139" s="41" t="s">
         <v>558</v>
       </c>
-      <c r="N139" s="41" t="s">
+      <c r="O139" s="16" t="s">
         <v>559</v>
-      </c>
-      <c r="O139" s="16" t="s">
-        <v>560</v>
       </c>
       <c r="P139" s="15" t="s">
         <v>71</v>
@@ -20252,10 +20257,10 @@
     </row>
     <row r="140" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A140" s="19" t="s">
+        <v>560</v>
+      </c>
+      <c r="B140" s="19" t="s">
         <v>561</v>
-      </c>
-      <c r="B140" s="19" t="s">
-        <v>562</v>
       </c>
       <c r="C140" s="65">
         <v>46185</v>
@@ -20264,19 +20269,19 @@
         <v>55</v>
       </c>
       <c r="E140" s="12" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F140" s="19" t="s">
+        <v>562</v>
+      </c>
+      <c r="G140" s="84" t="s">
+        <v>548</v>
+      </c>
+      <c r="H140" s="15" t="s">
+        <v>545</v>
+      </c>
+      <c r="I140" s="19" t="s">
         <v>563</v>
-      </c>
-      <c r="G140" s="84" t="s">
-        <v>549</v>
-      </c>
-      <c r="H140" s="15" t="s">
-        <v>546</v>
-      </c>
-      <c r="I140" s="19" t="s">
-        <v>564</v>
       </c>
       <c r="J140" s="19"/>
       <c r="K140" s="19"/>
@@ -20338,10 +20343,10 @@
     </row>
     <row r="141" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A141" s="19" t="s">
+        <v>564</v>
+      </c>
+      <c r="B141" s="117" t="s">
         <v>565</v>
-      </c>
-      <c r="B141" s="117" t="s">
-        <v>566</v>
       </c>
       <c r="C141" s="65">
         <v>46185</v>
@@ -20350,30 +20355,30 @@
         <v>55</v>
       </c>
       <c r="E141" s="12" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F141" s="19" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="G141" s="93" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H141" s="15" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="I141" s="16"/>
       <c r="K141" s="12"/>
       <c r="L141" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="N141" s="12" t="s">
         <v>568</v>
-      </c>
-      <c r="N141" s="12" t="s">
-        <v>569</v>
       </c>
       <c r="P141" s="15" t="s">
         <v>71</v>
       </c>
       <c r="Q141" s="16" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="R141" s="16"/>
       <c r="S141" s="16"/>
@@ -20396,10 +20401,10 @@
     </row>
     <row r="142" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A142" s="19" t="s">
+        <v>570</v>
+      </c>
+      <c r="B142" s="117" t="s">
         <v>571</v>
-      </c>
-      <c r="B142" s="117" t="s">
-        <v>572</v>
       </c>
       <c r="C142" s="65">
         <v>46185</v>
@@ -20408,16 +20413,16 @@
         <v>55</v>
       </c>
       <c r="E142" s="12" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F142" s="19" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="G142" s="93" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H142" s="15" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="I142" s="16"/>
       <c r="K142" s="12"/>
@@ -20447,10 +20452,10 @@
     </row>
     <row r="143" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A143" s="19" t="s">
+        <v>573</v>
+      </c>
+      <c r="B143" s="25" t="s">
         <v>574</v>
-      </c>
-      <c r="B143" s="25" t="s">
-        <v>575</v>
       </c>
       <c r="C143" s="65">
         <v>46185</v>
@@ -20459,22 +20464,22 @@
         <v>55</v>
       </c>
       <c r="E143" s="19" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F143" s="19" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="G143" s="114" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H143" s="15" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="I143" s="19"/>
       <c r="J143" s="19"/>
       <c r="K143" s="19"/>
       <c r="L143" s="4" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="M143" s="19"/>
       <c r="N143" s="19"/>
@@ -20487,7 +20492,7 @@
       </c>
       <c r="R143" s="19"/>
       <c r="S143" s="19" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="T143" s="19"/>
       <c r="U143" s="19"/>
@@ -20560,7 +20565,7 @@
     </row>
     <row r="144" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A144" s="19" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B144" s="82"/>
       <c r="C144" s="85">
@@ -20570,16 +20575,16 @@
         <v>55</v>
       </c>
       <c r="E144" s="19" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F144" s="19" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="G144" s="114" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H144" s="15" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="I144" s="16"/>
       <c r="J144" s="16"/>
@@ -20603,7 +20608,7 @@
         <v>210</v>
       </c>
       <c r="X144" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="Y144" s="16"/>
       <c r="Z144" s="16"/>
@@ -20629,13 +20634,13 @@
       <c r="AP144" s="82"/>
       <c r="AQ144" s="3"/>
       <c r="AR144" s="16" t="s">
+        <v>581</v>
+      </c>
+      <c r="AS144" s="16" t="s">
         <v>582</v>
       </c>
-      <c r="AS144" s="16" t="s">
+      <c r="AT144" s="16" t="s">
         <v>583</v>
-      </c>
-      <c r="AT144" s="16" t="s">
-        <v>584</v>
       </c>
       <c r="AU144" s="16"/>
       <c r="AV144" s="16"/>
@@ -20673,10 +20678,10 @@
     </row>
     <row r="145" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A145" s="16" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B145" s="55" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C145" s="13">
         <v>46185</v>
@@ -20685,19 +20690,19 @@
         <v>55</v>
       </c>
       <c r="E145" s="12" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="F145" s="16" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="G145" s="12" t="s">
+        <v>587</v>
+      </c>
+      <c r="H145" s="12" t="s">
         <v>588</v>
       </c>
-      <c r="H145" s="12" t="s">
+      <c r="I145" s="119" t="s">
         <v>589</v>
-      </c>
-      <c r="I145" s="119" t="s">
-        <v>590</v>
       </c>
       <c r="AP145" s="20" t="s">
         <v>74</v>
@@ -20711,10 +20716,10 @@
     </row>
     <row r="146" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A146" s="16" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C146" s="13">
         <v>46185</v>
@@ -20723,16 +20728,16 @@
         <v>55</v>
       </c>
       <c r="E146" s="12" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="F146" s="16" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="G146" s="12" t="s">
+        <v>587</v>
+      </c>
+      <c r="H146" s="12" t="s">
         <v>588</v>
-      </c>
-      <c r="H146" s="12" t="s">
-        <v>589</v>
       </c>
       <c r="AP146" s="20" t="s">
         <v>74</v>
@@ -20746,7 +20751,7 @@
     </row>
     <row r="147" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A147" s="16" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>74</v>
@@ -20758,16 +20763,16 @@
         <v>55</v>
       </c>
       <c r="E147" s="12" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="F147" s="16" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="G147" s="12" t="s">
+        <v>587</v>
+      </c>
+      <c r="H147" s="12" t="s">
         <v>588</v>
-      </c>
-      <c r="H147" s="12" t="s">
-        <v>589</v>
       </c>
       <c r="X147" s="16" t="s">
         <v>97</v>
@@ -20790,10 +20795,10 @@
     </row>
     <row r="148" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A148" s="16" t="s">
+        <v>591</v>
+      </c>
+      <c r="B148" s="83" t="s">
         <v>592</v>
-      </c>
-      <c r="B148" s="83" t="s">
-        <v>593</v>
       </c>
       <c r="C148" s="13">
         <v>46281</v>
@@ -20802,20 +20807,20 @@
         <v>55</v>
       </c>
       <c r="E148" s="12" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="F148" s="12" t="s">
+        <v>593</v>
+      </c>
+      <c r="G148" s="120" t="s">
         <v>594</v>
-      </c>
-      <c r="G148" s="120" t="s">
-        <v>595</v>
       </c>
       <c r="H148" s="100"/>
       <c r="J148" s="12" t="s">
         <v>170</v>
       </c>
       <c r="L148" s="4" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="Y148" s="12" t="s">
         <v>274</v>
@@ -20832,10 +20837,10 @@
     </row>
     <row r="149" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A149" s="16" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B149" s="20" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C149" s="13">
         <v>46281</v>
@@ -20844,13 +20849,13 @@
         <v>55</v>
       </c>
       <c r="E149" s="12" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="F149" s="12" t="s">
+        <v>593</v>
+      </c>
+      <c r="G149" s="120" t="s">
         <v>594</v>
-      </c>
-      <c r="G149" s="120" t="s">
-        <v>595</v>
       </c>
       <c r="H149" s="100"/>
       <c r="J149" s="12" t="s">
@@ -20858,13 +20863,13 @@
       </c>
       <c r="Y149" s="12"/>
       <c r="AA149" s="121" t="s">
+        <v>597</v>
+      </c>
+      <c r="AB149" s="12" t="s">
         <v>598</v>
       </c>
-      <c r="AB149" s="12" t="s">
+      <c r="AC149" s="12" t="s">
         <v>599</v>
-      </c>
-      <c r="AC149" s="12" t="s">
-        <v>600</v>
       </c>
       <c r="AH149" s="14"/>
       <c r="AJ149" s="12" t="s">
@@ -20879,7 +20884,7 @@
     </row>
     <row r="150" spans="1:75" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A150" s="16" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B150" s="91"/>
       <c r="C150" s="13">
@@ -20889,13 +20894,13 @@
         <v>55</v>
       </c>
       <c r="E150" s="12" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="F150" s="12" t="s">
+        <v>593</v>
+      </c>
+      <c r="G150" s="120" t="s">
         <v>594</v>
-      </c>
-      <c r="G150" s="120" t="s">
-        <v>595</v>
       </c>
       <c r="H150" s="100"/>
       <c r="J150" s="12" t="s">
@@ -20904,10 +20909,10 @@
       <c r="Y150" s="12"/>
       <c r="AC150" s="12"/>
       <c r="AR150" s="19" t="s">
+        <v>600</v>
+      </c>
+      <c r="AS150" s="19" t="s">
         <v>601</v>
-      </c>
-      <c r="AS150" s="19" t="s">
-        <v>602</v>
       </c>
       <c r="BA150" s="19" t="s">
         <v>62</v>
@@ -20916,10 +20921,10 @@
     </row>
     <row r="151" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A151" s="15" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B151" s="83" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C151" s="24">
         <v>46121</v>
@@ -20928,24 +20933,24 @@
         <v>55</v>
       </c>
       <c r="E151" s="19" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="F151" s="15" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G151" s="12" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H151" s="12" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="I151" s="55"/>
       <c r="J151" s="18" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="K151" s="16"/>
       <c r="L151" s="49" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="M151" s="16"/>
       <c r="N151" s="41"/>
@@ -20964,7 +20969,7 @@
       <c r="AJ151" s="16"/>
       <c r="AP151" s="72"/>
       <c r="AQ151" s="45" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AR151" s="14"/>
       <c r="AS151" s="14"/>
@@ -20973,10 +20978,10 @@
     </row>
     <row r="152" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A152" s="15" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B152" s="55" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C152" s="24">
         <v>46121</v>
@@ -20985,19 +20990,19 @@
         <v>55</v>
       </c>
       <c r="E152" s="19" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="F152" s="15" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G152" s="12" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H152" s="12" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="I152" s="55" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="J152" t="s">
         <v>170</v>
@@ -21021,7 +21026,7 @@
       <c r="AJ152" s="16"/>
       <c r="AP152" s="72"/>
       <c r="AQ152" s="45" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AR152" s="14"/>
       <c r="AS152" s="14"/>
@@ -21030,10 +21035,10 @@
     </row>
     <row r="153" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A153" s="15" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B153" s="57" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C153" s="24">
         <v>46121</v>
@@ -21042,31 +21047,31 @@
         <v>55</v>
       </c>
       <c r="E153" s="19" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="F153" s="15" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G153" s="12" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H153" s="12" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="I153" s="16"/>
       <c r="J153" s="122" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="K153" s="16"/>
       <c r="L153" s="16"/>
       <c r="M153" s="116" t="s">
+        <v>614</v>
+      </c>
+      <c r="N153" s="41" t="s">
         <v>615</v>
       </c>
-      <c r="N153" s="41" t="s">
+      <c r="O153" s="42" t="s">
         <v>616</v>
-      </c>
-      <c r="O153" s="42" t="s">
-        <v>617</v>
       </c>
       <c r="P153" s="15" t="s">
         <v>71</v>
@@ -21098,7 +21103,7 @@
         <v>100</v>
       </c>
       <c r="AQ153" s="45" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AR153" s="14"/>
       <c r="AS153" s="14"/>
@@ -21111,7 +21116,7 @@
     </row>
     <row r="154" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A154" s="15" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B154" s="124"/>
       <c r="C154" s="65">
@@ -21121,22 +21126,22 @@
         <v>55</v>
       </c>
       <c r="E154" s="19" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="F154" s="15" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G154" s="19" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H154" s="15" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="I154" s="15"/>
       <c r="J154" s="19"/>
       <c r="K154" s="41"/>
       <c r="L154" s="45" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="M154" s="41"/>
       <c r="N154" s="19"/>
@@ -21145,7 +21150,7 @@
         <v>71</v>
       </c>
       <c r="Q154" s="68" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="R154" s="15"/>
       <c r="S154" s="15"/>
@@ -21155,7 +21160,7 @@
       <c r="W154" s="19"/>
       <c r="X154" s="19"/>
       <c r="Y154" s="19" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="Z154" s="19"/>
       <c r="AA154" s="19"/>
@@ -21180,13 +21185,13 @@
       <c r="AP154" s="19"/>
       <c r="AQ154" s="15"/>
       <c r="AR154" s="19" t="s">
+        <v>600</v>
+      </c>
+      <c r="AS154" s="19" t="s">
         <v>601</v>
       </c>
-      <c r="AS154" s="19" t="s">
-        <v>602</v>
-      </c>
       <c r="AT154" s="19" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AU154" s="19"/>
       <c r="AV154" s="19"/>
@@ -21224,10 +21229,10 @@
     </row>
     <row r="155" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A155" s="12" t="s">
+        <v>621</v>
+      </c>
+      <c r="B155" s="20" t="s">
         <v>622</v>
-      </c>
-      <c r="B155" s="20" t="s">
-        <v>623</v>
       </c>
       <c r="C155" s="13">
         <v>46185</v>
@@ -21236,13 +21241,13 @@
         <v>55</v>
       </c>
       <c r="E155" s="12" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="F155" s="12" t="s">
+        <v>623</v>
+      </c>
+      <c r="G155" s="12" t="s">
         <v>624</v>
-      </c>
-      <c r="G155" s="12" t="s">
-        <v>625</v>
       </c>
       <c r="H155" s="100"/>
       <c r="J155" s="12" t="s">
@@ -21250,13 +21255,13 @@
       </c>
       <c r="Y155" s="14"/>
       <c r="AA155" s="121" t="s">
+        <v>597</v>
+      </c>
+      <c r="AB155" s="12" t="s">
         <v>598</v>
       </c>
-      <c r="AB155" s="12" t="s">
+      <c r="AC155" s="12" t="s">
         <v>599</v>
-      </c>
-      <c r="AC155" s="12" t="s">
-        <v>600</v>
       </c>
       <c r="AH155" s="14"/>
       <c r="AJ155" s="12" t="s">
@@ -21271,7 +21276,7 @@
     </row>
     <row r="156" spans="1:75" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A156" s="12" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B156" s="14"/>
       <c r="C156" s="13">
@@ -21281,13 +21286,13 @@
         <v>55</v>
       </c>
       <c r="E156" s="12" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="F156" s="12" t="s">
+        <v>623</v>
+      </c>
+      <c r="G156" s="12" t="s">
         <v>624</v>
-      </c>
-      <c r="G156" s="12" t="s">
-        <v>625</v>
       </c>
       <c r="H156" s="100"/>
       <c r="AR156" s="100"/>
@@ -21299,10 +21304,10 @@
     </row>
     <row r="157" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A157" s="12" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B157" s="20" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C157" s="13">
         <v>46185</v>
@@ -21311,23 +21316,23 @@
         <v>55</v>
       </c>
       <c r="E157" s="12" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F157" s="12" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="J157" s="12" t="s">
         <v>170</v>
       </c>
       <c r="Y157" s="14"/>
       <c r="AA157" s="121" t="s">
+        <v>597</v>
+      </c>
+      <c r="AB157" s="12" t="s">
         <v>598</v>
       </c>
-      <c r="AB157" s="12" t="s">
+      <c r="AC157" s="12" t="s">
         <v>599</v>
-      </c>
-      <c r="AC157" s="12" t="s">
-        <v>600</v>
       </c>
       <c r="AH157" s="14"/>
       <c r="AJ157" s="12" t="s">
@@ -21340,10 +21345,10 @@
     </row>
     <row r="158" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A158" s="25" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B158" s="57" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C158" s="125">
         <v>46185</v>
@@ -21352,22 +21357,22 @@
         <v>55</v>
       </c>
       <c r="E158" s="25" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F158" s="25" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="G158" s="126" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H158" s="57" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="I158" s="57"/>
       <c r="J158" s="25"/>
       <c r="K158" s="25"/>
       <c r="L158" s="4" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="M158" s="25"/>
       <c r="N158" s="25"/>
@@ -21401,7 +21406,7 @@
         <v>87</v>
       </c>
       <c r="AJ158" s="25" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="AK158" s="25"/>
       <c r="AL158" s="25"/>
@@ -21451,10 +21456,10 @@
     </row>
     <row r="159" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A159" s="12" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B159" s="20" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C159" s="13">
         <v>46185</v>
@@ -21463,22 +21468,22 @@
         <v>55</v>
       </c>
       <c r="E159" s="12" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F159" s="16" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="G159" s="100"/>
       <c r="H159" s="100"/>
       <c r="Y159" s="14"/>
       <c r="AA159" s="121" t="s">
+        <v>597</v>
+      </c>
+      <c r="AB159" s="12" t="s">
         <v>598</v>
       </c>
-      <c r="AB159" s="12" t="s">
+      <c r="AC159" s="12" t="s">
         <v>599</v>
-      </c>
-      <c r="AC159" s="12" t="s">
-        <v>600</v>
       </c>
       <c r="AJ159" s="12" t="s">
         <v>175</v>
@@ -21490,10 +21495,10 @@
     </row>
     <row r="160" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A160" s="12" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B160" s="83" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C160" s="13">
         <v>46185</v>
@@ -21502,10 +21507,10 @@
         <v>55</v>
       </c>
       <c r="E160" s="12" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F160" s="16" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="G160" s="100"/>
       <c r="H160" s="100"/>
@@ -21531,10 +21536,10 @@
     </row>
     <row r="161" spans="1:55" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A161" s="12" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B161" s="129" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C161" s="13">
         <v>46185</v>
@@ -21543,21 +21548,21 @@
         <v>55</v>
       </c>
       <c r="E161" s="16" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F161" s="16" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="G161" s="100"/>
       <c r="H161" s="100"/>
       <c r="Y161" s="12" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AI161" s="31" t="s">
         <v>87</v>
       </c>
       <c r="AJ161" s="12" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="BA161" s="19" t="s">
         <v>62</v>
@@ -21566,10 +21571,10 @@
     </row>
     <row r="162" spans="1:55" ht="13" x14ac:dyDescent="0.3">
       <c r="A162" s="16" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B162" s="12" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C162" s="13">
         <v>46185</v>
@@ -21578,10 +21583,10 @@
         <v>55</v>
       </c>
       <c r="E162" s="16" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F162" s="12" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="G162" s="100"/>
       <c r="H162" s="100"/>
@@ -21598,10 +21603,10 @@
     </row>
     <row r="163" spans="1:55" ht="13" x14ac:dyDescent="0.3">
       <c r="A163" s="16" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B163" s="12" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C163" s="13">
         <v>46185</v>
@@ -21610,10 +21615,10 @@
         <v>55</v>
       </c>
       <c r="E163" s="16" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F163" s="12" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="G163" s="100"/>
       <c r="H163" s="100"/>
@@ -21630,10 +21635,10 @@
     </row>
     <row r="164" spans="1:55" ht="13" x14ac:dyDescent="0.3">
       <c r="A164" s="16" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B164" s="20" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C164" s="13">
         <v>46185</v>
@@ -21642,22 +21647,22 @@
         <v>55</v>
       </c>
       <c r="E164" s="16" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F164" s="16" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="G164" s="100"/>
       <c r="H164" s="100"/>
       <c r="Y164" s="14"/>
       <c r="AA164" s="121" t="s">
+        <v>597</v>
+      </c>
+      <c r="AB164" s="12" t="s">
         <v>598</v>
       </c>
-      <c r="AB164" s="12" t="s">
+      <c r="AC164" s="12" t="s">
         <v>599</v>
-      </c>
-      <c r="AC164" s="12" t="s">
-        <v>600</v>
       </c>
       <c r="AJ164" s="12" t="s">
         <v>175</v>
@@ -21669,7 +21674,7 @@
     </row>
     <row r="165" spans="1:55" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A165" s="16" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C165" s="13">
         <v>46185</v>
@@ -21678,10 +21683,10 @@
         <v>55</v>
       </c>
       <c r="E165" s="16" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F165" s="16" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="G165" s="100"/>
       <c r="H165" s="100"/>
@@ -21692,7 +21697,7 @@
     </row>
     <row r="166" spans="1:55" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A166" s="16" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C166" s="13">
         <v>46185</v>
@@ -21701,10 +21706,10 @@
         <v>55</v>
       </c>
       <c r="E166" s="16" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F166" s="16" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="G166" s="100"/>
       <c r="H166" s="100"/>
@@ -21715,10 +21720,10 @@
     </row>
     <row r="167" spans="1:55" ht="13" x14ac:dyDescent="0.3">
       <c r="A167" s="16" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B167" s="130" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C167" s="13">
         <v>46185</v>
@@ -21727,15 +21732,15 @@
         <v>55</v>
       </c>
       <c r="E167" s="16" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F167" s="12" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G167" s="100"/>
       <c r="H167" s="100"/>
       <c r="S167" s="12" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="Y167" s="12" t="s">
         <v>178</v>
@@ -21752,7 +21757,7 @@
     </row>
     <row r="168" spans="1:55" ht="13" x14ac:dyDescent="0.3">
       <c r="A168" s="16" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B168" s="39"/>
       <c r="C168" s="13">
@@ -21762,10 +21767,10 @@
         <v>55</v>
       </c>
       <c r="E168" s="16" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F168" s="12" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G168" s="100"/>
       <c r="H168" s="100"/>
@@ -21776,7 +21781,7 @@
         <v>92</v>
       </c>
       <c r="AR168" s="12" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="BA168" s="19" t="s">
         <v>62</v>
@@ -21785,10 +21790,10 @@
     </row>
     <row r="169" spans="1:55" ht="13" x14ac:dyDescent="0.3">
       <c r="A169" s="16" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B169" s="130" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C169" s="13">
         <v>46185</v>
@@ -21797,10 +21802,10 @@
         <v>55</v>
       </c>
       <c r="E169" s="16" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F169" s="16" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="G169" s="100"/>
       <c r="H169" s="100"/>
@@ -21817,10 +21822,10 @@
     </row>
     <row r="170" spans="1:55" ht="13" x14ac:dyDescent="0.3">
       <c r="A170" s="16" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B170" s="130" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C170" s="13">
         <v>46185</v>
@@ -21829,10 +21834,10 @@
         <v>55</v>
       </c>
       <c r="E170" s="16" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F170" s="16" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="G170" s="100"/>
       <c r="H170" s="100"/>
@@ -21846,10 +21851,10 @@
     </row>
     <row r="171" spans="1:55" ht="13" x14ac:dyDescent="0.3">
       <c r="A171" s="16" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B171" s="130" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C171" s="13">
         <v>46185</v>
@@ -21858,10 +21863,10 @@
         <v>55</v>
       </c>
       <c r="E171" s="16" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F171" s="16" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="G171" s="100"/>
       <c r="H171" s="100"/>
@@ -21878,7 +21883,7 @@
     </row>
     <row r="172" spans="1:55" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A172" s="16" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B172" s="14"/>
       <c r="C172" s="13">
@@ -21888,10 +21893,10 @@
         <v>55</v>
       </c>
       <c r="E172" s="16" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F172" s="16" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="G172" s="100"/>
       <c r="H172" s="100"/>
@@ -21902,7 +21907,7 @@
     </row>
     <row r="173" spans="1:55" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A173" s="16" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C173" s="13">
         <v>46185</v>
@@ -21911,10 +21916,10 @@
         <v>55</v>
       </c>
       <c r="E173" s="16" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F173" s="12" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G173" s="100"/>
       <c r="H173" s="100"/>
@@ -21925,7 +21930,7 @@
     </row>
     <row r="174" spans="1:55" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A174" s="16" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C174" s="13">
         <v>46185</v>
@@ -21934,10 +21939,10 @@
         <v>55</v>
       </c>
       <c r="E174" s="16" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F174" s="12" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G174" s="100"/>
       <c r="H174" s="100"/>
@@ -21948,7 +21953,7 @@
     </row>
     <row r="175" spans="1:55" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A175" s="16" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C175" s="13">
         <v>46185</v>
@@ -21957,10 +21962,10 @@
         <v>55</v>
       </c>
       <c r="E175" s="16" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F175" s="16" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="G175" s="100"/>
       <c r="H175" s="100"/>
@@ -21971,10 +21976,10 @@
     </row>
     <row r="176" spans="1:55" ht="13" x14ac:dyDescent="0.3">
       <c r="A176" s="16" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B176" s="130" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C176" s="13">
         <v>46185</v>
@@ -21983,10 +21988,10 @@
         <v>55</v>
       </c>
       <c r="E176" s="16" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F176" s="16" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="G176" s="100"/>
       <c r="H176" s="100"/>
@@ -22000,7 +22005,7 @@
     </row>
     <row r="177" spans="1:55" ht="13" x14ac:dyDescent="0.3">
       <c r="A177" s="16" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B177" s="39"/>
       <c r="C177" s="13">
@@ -22010,10 +22015,10 @@
         <v>55</v>
       </c>
       <c r="E177" s="16" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F177" s="16" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="G177" s="100"/>
       <c r="H177" s="100"/>
@@ -22023,10 +22028,10 @@
     </row>
     <row r="178" spans="1:55" ht="13" x14ac:dyDescent="0.3">
       <c r="A178" s="16" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B178" s="83" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C178" s="13">
         <v>46185</v>
@@ -22035,10 +22040,10 @@
         <v>55</v>
       </c>
       <c r="E178" s="16" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F178" s="12" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="G178" s="100"/>
       <c r="H178" s="100"/>
@@ -22052,7 +22057,7 @@
         <v>59</v>
       </c>
       <c r="AF178" s="72" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="AI178" s="31" t="s">
         <v>275</v>
@@ -22067,10 +22072,10 @@
     </row>
     <row r="179" spans="1:55" ht="13" x14ac:dyDescent="0.3">
       <c r="A179" s="16" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B179" s="119" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C179" s="13">
         <v>46185</v>
@@ -22079,10 +22084,10 @@
         <v>55</v>
       </c>
       <c r="E179" s="16" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F179" s="12" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="G179" s="100"/>
       <c r="H179" s="100"/>
@@ -22105,10 +22110,10 @@
     </row>
     <row r="180" spans="1:55" ht="13" x14ac:dyDescent="0.3">
       <c r="A180" s="16" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B180" s="130" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C180" s="13">
         <v>46185</v>
@@ -22117,10 +22122,10 @@
         <v>55</v>
       </c>
       <c r="E180" s="16" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F180" s="12" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="G180" s="100"/>
       <c r="H180" s="100"/>
@@ -22137,7 +22142,7 @@
     </row>
     <row r="181" spans="1:55" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A181" s="16" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C181" s="13">
         <v>46185</v>
@@ -22146,10 +22151,10 @@
         <v>55</v>
       </c>
       <c r="E181" s="16" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F181" s="12" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G181" s="100"/>
       <c r="H181" s="100"/>
@@ -22160,7 +22165,7 @@
     </row>
     <row r="182" spans="1:55" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A182" s="16" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C182" s="13">
         <v>46185</v>
@@ -22169,10 +22174,10 @@
         <v>55</v>
       </c>
       <c r="E182" s="16" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F182" s="12" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G182" s="100"/>
       <c r="H182" s="100"/>
@@ -22183,10 +22188,10 @@
     </row>
     <row r="183" spans="1:55" ht="13" x14ac:dyDescent="0.3">
       <c r="A183" s="16" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B183" s="95" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C183" s="13">
         <v>46185</v>
@@ -22195,15 +22200,15 @@
         <v>55</v>
       </c>
       <c r="E183" s="16" t="s">
+        <v>666</v>
+      </c>
+      <c r="F183" s="16" t="s">
         <v>667</v>
-      </c>
-      <c r="F183" s="16" t="s">
-        <v>668</v>
       </c>
       <c r="G183" s="100"/>
       <c r="H183" s="100"/>
       <c r="N183" s="19" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="X183" s="12" t="s">
         <v>273</v>
@@ -22227,10 +22232,10 @@
     </row>
     <row r="184" spans="1:55" ht="13" x14ac:dyDescent="0.3">
       <c r="A184" s="16" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B184" s="95" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C184" s="13">
         <v>46185</v>
@@ -22239,15 +22244,15 @@
         <v>55</v>
       </c>
       <c r="E184" s="16" t="s">
+        <v>666</v>
+      </c>
+      <c r="F184" s="16" t="s">
         <v>667</v>
-      </c>
-      <c r="F184" s="16" t="s">
-        <v>668</v>
       </c>
       <c r="G184" s="100"/>
       <c r="H184" s="100"/>
       <c r="N184" s="19" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="X184" s="12" t="s">
         <v>273</v>
@@ -22271,7 +22276,7 @@
     </row>
     <row r="185" spans="1:55" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A185" s="16" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B185" s="14"/>
       <c r="C185" s="13">
@@ -22281,10 +22286,10 @@
         <v>55</v>
       </c>
       <c r="E185" s="16" t="s">
+        <v>666</v>
+      </c>
+      <c r="F185" s="16" t="s">
         <v>667</v>
-      </c>
-      <c r="F185" s="16" t="s">
-        <v>668</v>
       </c>
       <c r="G185" s="100"/>
       <c r="H185" s="100"/>
@@ -22299,10 +22304,10 @@
     </row>
     <row r="186" spans="1:55" ht="13" x14ac:dyDescent="0.3">
       <c r="A186" s="16" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B186" s="95" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C186" s="13">
         <v>46185</v>
@@ -22311,15 +22316,15 @@
         <v>55</v>
       </c>
       <c r="E186" s="16" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="F186" s="16" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="G186" s="100"/>
       <c r="H186" s="100"/>
       <c r="N186" s="19" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="X186" s="12" t="s">
         <v>273</v>
@@ -22343,10 +22348,10 @@
     </row>
     <row r="187" spans="1:55" ht="13" x14ac:dyDescent="0.3">
       <c r="A187" s="16" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B187" s="19" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C187" s="13">
         <v>46185</v>
@@ -22355,15 +22360,15 @@
         <v>55</v>
       </c>
       <c r="E187" s="16" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="F187" s="16" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="G187" s="100"/>
       <c r="H187" s="100"/>
       <c r="N187" s="131" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="X187" s="12" t="s">
         <v>273</v>
@@ -22384,7 +22389,7 @@
     </row>
     <row r="188" spans="1:55" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A188" s="16" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B188" s="14"/>
       <c r="C188" s="13">
@@ -22394,10 +22399,10 @@
         <v>55</v>
       </c>
       <c r="E188" s="16" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="F188" s="16" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="G188" s="100"/>
       <c r="H188" s="100"/>
@@ -22408,7 +22413,7 @@
     </row>
     <row r="189" spans="1:55" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A189" s="16" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B189" s="19"/>
       <c r="C189" s="13">
@@ -22418,10 +22423,10 @@
         <v>55</v>
       </c>
       <c r="E189" s="16" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="F189" s="30" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="G189" s="100"/>
       <c r="H189" s="100"/>
@@ -22435,10 +22440,10 @@
     </row>
     <row r="190" spans="1:55" ht="13" x14ac:dyDescent="0.3">
       <c r="A190" s="16" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B190" s="95" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C190" s="13">
         <v>46185</v>
@@ -22447,15 +22452,15 @@
         <v>55</v>
       </c>
       <c r="E190" s="16" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="F190" s="30" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="G190" s="100"/>
       <c r="H190" s="100"/>
       <c r="N190" s="131" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="X190" s="12" t="s">
         <v>273</v>
@@ -22476,7 +22481,7 @@
     </row>
     <row r="191" spans="1:55" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A191" s="16" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B191" s="14"/>
       <c r="C191" s="13">
@@ -22486,10 +22491,10 @@
         <v>55</v>
       </c>
       <c r="E191" s="16" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="F191" s="30" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="G191" s="100"/>
       <c r="H191" s="100"/>
@@ -22497,44 +22502,44 @@
     </row>
     <row r="192" spans="1:55" ht="13" x14ac:dyDescent="0.3">
       <c r="A192" s="76" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B192" s="63" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C192" s="13">
         <v>46185</v>
       </c>
       <c r="D192" s="132" t="s">
+        <v>682</v>
+      </c>
+      <c r="E192" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="E192" s="16" t="s">
+      <c r="F192" s="76" t="s">
         <v>684</v>
       </c>
-      <c r="F192" s="76" t="s">
-        <v>685</v>
-      </c>
       <c r="G192" s="16" t="s">
+        <v>687</v>
+      </c>
+      <c r="H192" s="12" t="s">
         <v>688</v>
-      </c>
-      <c r="H192" s="12" t="s">
-        <v>689</v>
       </c>
       <c r="J192" s="16" t="s">
         <v>170</v>
       </c>
       <c r="K192" s="133" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="L192" s="12"/>
       <c r="M192" s="40" t="s">
+        <v>690</v>
+      </c>
+      <c r="N192" s="63" t="s">
         <v>691</v>
       </c>
-      <c r="N192" s="63" t="s">
+      <c r="O192" s="16" t="s">
         <v>692</v>
-      </c>
-      <c r="O192" s="16" t="s">
-        <v>693</v>
       </c>
       <c r="P192" s="15" t="s">
         <v>71</v>
@@ -22583,7 +22588,7 @@
       <c r="AX192" s="16"/>
       <c r="AY192" s="16"/>
       <c r="AZ192" s="16" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="BA192" s="19" t="s">
         <v>62</v>
@@ -22592,43 +22597,43 @@
     </row>
     <row r="193" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A193" s="76" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B193" s="20" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C193" s="13">
         <v>46185</v>
       </c>
       <c r="D193" s="132" t="s">
+        <v>682</v>
+      </c>
+      <c r="E193" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="E193" s="16" t="s">
+      <c r="F193" s="76" t="s">
         <v>684</v>
       </c>
-      <c r="F193" s="76" t="s">
+      <c r="G193" s="16" t="s">
         <v>685</v>
       </c>
-      <c r="G193" s="16" t="s">
-        <v>686</v>
-      </c>
       <c r="H193" s="12" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="J193" s="16" t="s">
         <v>170</v>
       </c>
       <c r="K193" s="79" t="s">
+        <v>696</v>
+      </c>
+      <c r="L193" s="72" t="s">
         <v>697</v>
       </c>
-      <c r="L193" s="72" t="s">
+      <c r="M193" s="40" t="s">
         <v>698</v>
       </c>
-      <c r="M193" s="40" t="s">
+      <c r="O193" s="16" t="s">
         <v>699</v>
-      </c>
-      <c r="O193" s="16" t="s">
-        <v>700</v>
       </c>
       <c r="P193" s="15" t="s">
         <v>71</v>
@@ -22643,10 +22648,10 @@
         <v>73</v>
       </c>
       <c r="AJ193" s="12" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AZ193" s="12" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="BA193" s="19" t="s">
         <v>62</v>
@@ -22676,39 +22681,39 @@
     </row>
     <row r="194" spans="1:75" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A194" s="76" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B194" s="12" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C194" s="13">
         <v>46185</v>
       </c>
       <c r="D194" s="132" t="s">
+        <v>682</v>
+      </c>
+      <c r="E194" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="E194" s="16" t="s">
+      <c r="F194" s="76" t="s">
         <v>684</v>
       </c>
-      <c r="F194" s="76" t="s">
-        <v>685</v>
-      </c>
       <c r="G194" s="16" t="s">
+        <v>701</v>
+      </c>
+      <c r="H194" s="12" t="s">
         <v>702</v>
-      </c>
-      <c r="H194" s="12" t="s">
-        <v>703</v>
       </c>
       <c r="J194" s="134"/>
       <c r="K194" s="79" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="L194" s="12"/>
       <c r="M194" s="40" t="s">
+        <v>704</v>
+      </c>
+      <c r="O194" s="135" t="s">
         <v>705</v>
-      </c>
-      <c r="O194" s="135" t="s">
-        <v>706</v>
       </c>
       <c r="P194" s="15" t="s">
         <v>71</v>
@@ -22720,7 +22725,7 @@
         <v>171</v>
       </c>
       <c r="Y194" s="12" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="AH194" s="16" t="s">
         <v>174</v>
@@ -22732,7 +22737,7 @@
         <v>175</v>
       </c>
       <c r="AZ194" s="12" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="BA194" s="19" t="s">
         <v>62</v>
@@ -22762,39 +22767,39 @@
     </row>
     <row r="195" spans="1:75" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A195" s="76" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B195" s="12" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C195" s="13">
         <v>46185</v>
       </c>
       <c r="D195" s="132" t="s">
+        <v>682</v>
+      </c>
+      <c r="E195" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="E195" s="16" t="s">
+      <c r="F195" s="76" t="s">
         <v>684</v>
       </c>
-      <c r="F195" s="76" t="s">
-        <v>685</v>
-      </c>
       <c r="G195" s="16" t="s">
+        <v>708</v>
+      </c>
+      <c r="H195" s="12" t="s">
         <v>709</v>
-      </c>
-      <c r="H195" s="12" t="s">
-        <v>710</v>
       </c>
       <c r="J195" s="134"/>
       <c r="K195" s="79" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="L195" s="12"/>
       <c r="M195" s="40" t="s">
+        <v>711</v>
+      </c>
+      <c r="O195" s="135" t="s">
         <v>712</v>
-      </c>
-      <c r="O195" s="135" t="s">
-        <v>713</v>
       </c>
       <c r="P195" s="15" t="s">
         <v>71</v>
@@ -22806,7 +22811,7 @@
         <v>171</v>
       </c>
       <c r="Y195" s="12" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="AH195" s="16" t="s">
         <v>174</v>
@@ -22818,7 +22823,7 @@
         <v>175</v>
       </c>
       <c r="AZ195" s="12" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="BA195" s="19" t="s">
         <v>62</v>
@@ -22827,44 +22832,44 @@
     </row>
     <row r="196" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A196" s="76" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B196" s="41" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C196" s="13">
         <v>46185</v>
       </c>
       <c r="D196" s="132" t="s">
+        <v>682</v>
+      </c>
+      <c r="E196" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="E196" s="16" t="s">
+      <c r="F196" s="76" t="s">
         <v>684</v>
       </c>
-      <c r="F196" s="76" t="s">
+      <c r="G196" s="16" t="s">
         <v>685</v>
       </c>
-      <c r="G196" s="16" t="s">
-        <v>686</v>
-      </c>
       <c r="H196" s="12" t="s">
+        <v>714</v>
+      </c>
+      <c r="I196" s="136" t="s">
         <v>715</v>
-      </c>
-      <c r="I196" s="136" t="s">
-        <v>716</v>
       </c>
       <c r="J196" s="137"/>
       <c r="K196" s="79" t="s">
+        <v>716</v>
+      </c>
+      <c r="L196" s="12" t="s">
         <v>717</v>
       </c>
-      <c r="L196" s="12" t="s">
+      <c r="N196" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="N196" s="12" t="s">
+      <c r="P196" s="12" t="s">
         <v>719</v>
-      </c>
-      <c r="P196" s="12" t="s">
-        <v>720</v>
       </c>
       <c r="Q196" s="135" t="s">
         <v>70</v>
@@ -22873,10 +22878,10 @@
         <v>274</v>
       </c>
       <c r="AA196" s="18" t="s">
+        <v>720</v>
+      </c>
+      <c r="AB196" s="12" t="s">
         <v>721</v>
-      </c>
-      <c r="AB196" s="12" t="s">
-        <v>722</v>
       </c>
       <c r="AC196" s="12" t="s">
         <v>59</v>
@@ -22886,10 +22891,10 @@
         <v>87</v>
       </c>
       <c r="AJ196" s="12" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="AZ196" s="12" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="BA196" s="19" t="s">
         <v>62</v>
@@ -22898,45 +22903,45 @@
     </row>
     <row r="197" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A197" s="76" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B197" s="138" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C197" s="139">
         <v>46185</v>
       </c>
       <c r="D197" s="140" t="s">
+        <v>682</v>
+      </c>
+      <c r="E197" s="15" t="s">
         <v>683</v>
       </c>
-      <c r="E197" s="15" t="s">
+      <c r="F197" s="76" t="s">
         <v>684</v>
       </c>
-      <c r="F197" s="76" t="s">
+      <c r="G197" s="15" t="s">
         <v>685</v>
       </c>
-      <c r="G197" s="15" t="s">
-        <v>686</v>
-      </c>
       <c r="H197" s="19" t="s">
+        <v>724</v>
+      </c>
+      <c r="I197" s="135" t="s">
         <v>725</v>
-      </c>
-      <c r="I197" s="135" t="s">
-        <v>726</v>
       </c>
       <c r="J197" s="141"/>
       <c r="K197" s="142" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="L197" s="76"/>
       <c r="M197" s="143" t="s">
+        <v>727</v>
+      </c>
+      <c r="N197" s="138" t="s">
         <v>728</v>
       </c>
-      <c r="N197" s="138" t="s">
+      <c r="O197" s="135" t="s">
         <v>729</v>
-      </c>
-      <c r="O197" s="135" t="s">
-        <v>730</v>
       </c>
       <c r="P197" s="76" t="s">
         <v>71</v>
@@ -22959,7 +22964,7 @@
       <c r="AA197" s="76"/>
       <c r="AB197" s="76"/>
       <c r="AC197" s="12" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="AD197" s="76"/>
       <c r="AE197" s="76"/>
@@ -22990,7 +22995,7 @@
       <c r="AX197" s="76"/>
       <c r="AY197" s="76"/>
       <c r="AZ197" s="12" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="BA197" s="19" t="s">
         <v>62</v>
@@ -23020,45 +23025,45 @@
     </row>
     <row r="198" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A198" s="76" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B198" s="20" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C198" s="13">
         <v>46185</v>
       </c>
       <c r="D198" s="132" t="s">
+        <v>682</v>
+      </c>
+      <c r="E198" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="E198" s="16" t="s">
+      <c r="F198" s="76" t="s">
         <v>684</v>
       </c>
-      <c r="F198" s="76" t="s">
-        <v>685</v>
-      </c>
       <c r="G198" s="16" t="s">
+        <v>732</v>
+      </c>
+      <c r="H198" s="12" t="s">
         <v>733</v>
       </c>
-      <c r="H198" s="12" t="s">
-        <v>734</v>
-      </c>
       <c r="I198" s="30" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="J198" s="137"/>
       <c r="K198" s="79" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="L198" s="12"/>
       <c r="M198" s="40" t="s">
+        <v>735</v>
+      </c>
+      <c r="N198" s="63" t="s">
+        <v>728</v>
+      </c>
+      <c r="O198" s="135" t="s">
         <v>736</v>
-      </c>
-      <c r="N198" s="63" t="s">
-        <v>729</v>
-      </c>
-      <c r="O198" s="135" t="s">
-        <v>737</v>
       </c>
       <c r="P198" s="15" t="s">
         <v>71</v>
@@ -23074,7 +23079,7 @@
         <v>125</v>
       </c>
       <c r="AC198" s="12" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="AH198" s="15" t="s">
         <v>126</v>
@@ -23086,7 +23091,7 @@
         <v>127</v>
       </c>
       <c r="AZ198" s="12" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="BA198" s="19" t="s">
         <v>62</v>
@@ -23095,45 +23100,45 @@
     </row>
     <row r="199" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A199" s="76" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B199" s="20" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C199" s="13">
         <v>46185</v>
       </c>
       <c r="D199" s="132" t="s">
+        <v>682</v>
+      </c>
+      <c r="E199" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="E199" s="16" t="s">
+      <c r="F199" s="76" t="s">
         <v>684</v>
       </c>
-      <c r="F199" s="76" t="s">
-        <v>685</v>
-      </c>
       <c r="G199" s="16" t="s">
+        <v>732</v>
+      </c>
+      <c r="H199" s="12" t="s">
         <v>733</v>
-      </c>
-      <c r="H199" s="12" t="s">
-        <v>734</v>
       </c>
       <c r="I199" s="52"/>
       <c r="J199" s="16" t="s">
         <v>170</v>
       </c>
       <c r="K199" s="79" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="L199" s="12"/>
       <c r="M199" s="40" t="s">
+        <v>739</v>
+      </c>
+      <c r="N199" s="63" t="s">
+        <v>728</v>
+      </c>
+      <c r="O199" s="30" t="s">
         <v>740</v>
-      </c>
-      <c r="N199" s="63" t="s">
-        <v>729</v>
-      </c>
-      <c r="O199" s="30" t="s">
-        <v>741</v>
       </c>
       <c r="P199" s="15" t="s">
         <v>71</v>
@@ -23149,7 +23154,7 @@
         <v>125</v>
       </c>
       <c r="AC199" s="12" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="AH199" s="15" t="s">
         <v>126</v>
@@ -23161,7 +23166,7 @@
         <v>127</v>
       </c>
       <c r="AZ199" s="12" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="BA199" s="19" t="s">
         <v>62</v>
@@ -23170,40 +23175,40 @@
     </row>
     <row r="200" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A200" s="76" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B200" s="63" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C200" s="13">
         <v>46200</v>
       </c>
       <c r="D200" s="132" t="s">
+        <v>682</v>
+      </c>
+      <c r="E200" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="E200" s="16" t="s">
+      <c r="F200" s="76" t="s">
         <v>684</v>
       </c>
-      <c r="F200" s="76" t="s">
-        <v>685</v>
-      </c>
       <c r="G200" s="16" t="s">
+        <v>732</v>
+      </c>
+      <c r="H200" s="12" t="s">
         <v>733</v>
       </c>
-      <c r="H200" s="12" t="s">
-        <v>734</v>
-      </c>
       <c r="J200" s="72" t="s">
+        <v>742</v>
+      </c>
+      <c r="K200" s="79" t="s">
         <v>743</v>
       </c>
-      <c r="K200" s="79" t="s">
+      <c r="L200" s="18" t="s">
         <v>744</v>
       </c>
-      <c r="L200" s="18" t="s">
+      <c r="M200" s="40" t="s">
         <v>745</v>
-      </c>
-      <c r="M200" s="40" t="s">
-        <v>746</v>
       </c>
       <c r="N200" s="16"/>
       <c r="O200" s="16"/>
@@ -23244,7 +23249,7 @@
       <c r="AX200" s="16"/>
       <c r="AY200" s="16"/>
       <c r="AZ200" s="12" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="BA200" s="19" t="s">
         <v>62</v>
@@ -23253,26 +23258,26 @@
     </row>
     <row r="201" spans="1:75" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A201" s="76" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B201" s="14"/>
       <c r="C201" s="13">
         <v>46200</v>
       </c>
       <c r="D201" s="132" t="s">
+        <v>682</v>
+      </c>
+      <c r="E201" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="E201" s="16" t="s">
+      <c r="F201" s="76" t="s">
         <v>684</v>
       </c>
-      <c r="F201" s="76" t="s">
-        <v>685</v>
-      </c>
       <c r="G201" s="16" t="s">
+        <v>732</v>
+      </c>
+      <c r="H201" s="12" t="s">
         <v>733</v>
-      </c>
-      <c r="H201" s="12" t="s">
-        <v>734</v>
       </c>
       <c r="I201" s="15"/>
       <c r="J201" s="144"/>
@@ -23296,7 +23301,7 @@
         <v>210</v>
       </c>
       <c r="X201" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="Y201" s="16"/>
       <c r="Z201" s="16"/>
@@ -23322,11 +23327,11 @@
       <c r="AP201" s="16"/>
       <c r="AQ201" s="3"/>
       <c r="AR201" s="16" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="AS201" s="16"/>
       <c r="AT201" s="16" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="AU201" s="16"/>
       <c r="AV201" s="16"/>
@@ -23334,7 +23339,7 @@
       <c r="AX201" s="16"/>
       <c r="AY201" s="16"/>
       <c r="AZ201" s="12" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="BA201" s="19" t="s">
         <v>62</v>
@@ -23364,26 +23369,26 @@
     </row>
     <row r="202" spans="1:75" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A202" s="76" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B202" s="14"/>
       <c r="C202" s="13">
         <v>46200</v>
       </c>
       <c r="D202" s="132" t="s">
+        <v>682</v>
+      </c>
+      <c r="E202" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="E202" s="16" t="s">
+      <c r="F202" s="76" t="s">
         <v>684</v>
       </c>
-      <c r="F202" s="76" t="s">
-        <v>685</v>
-      </c>
       <c r="G202" s="16" t="s">
+        <v>732</v>
+      </c>
+      <c r="H202" s="12" t="s">
         <v>733</v>
-      </c>
-      <c r="H202" s="12" t="s">
-        <v>734</v>
       </c>
       <c r="I202" s="16"/>
       <c r="J202" s="16"/>
@@ -23407,7 +23412,7 @@
         <v>210</v>
       </c>
       <c r="X202" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="Y202" s="16"/>
       <c r="Z202" s="16"/>
@@ -23433,13 +23438,13 @@
       <c r="AP202" s="16"/>
       <c r="AQ202" s="3"/>
       <c r="AR202" s="16" t="s">
+        <v>748</v>
+      </c>
+      <c r="AS202" s="16" t="s">
         <v>749</v>
       </c>
-      <c r="AS202" s="16" t="s">
+      <c r="AT202" t="s">
         <v>750</v>
-      </c>
-      <c r="AT202" t="s">
-        <v>751</v>
       </c>
       <c r="AU202" s="16"/>
       <c r="AV202" s="16"/>
@@ -23447,7 +23452,7 @@
       <c r="AX202" s="16"/>
       <c r="AY202" s="16"/>
       <c r="AZ202" s="12" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="BA202" s="19" t="s">
         <v>62</v>
@@ -23477,44 +23482,44 @@
     </row>
     <row r="203" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A203" s="12" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B203" s="63" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C203" s="13">
         <v>46185</v>
       </c>
       <c r="D203" s="132" t="s">
+        <v>682</v>
+      </c>
+      <c r="E203" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="E203" s="16" t="s">
-        <v>684</v>
-      </c>
       <c r="F203" s="12" t="s">
+        <v>752</v>
+      </c>
+      <c r="G203" s="145" t="s">
         <v>753</v>
       </c>
-      <c r="G203" s="145" t="s">
-        <v>754</v>
-      </c>
       <c r="H203" s="16" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="J203" s="16" t="s">
         <v>170</v>
       </c>
       <c r="K203" s="133" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="L203" s="12"/>
       <c r="M203" s="40" t="s">
+        <v>690</v>
+      </c>
+      <c r="N203" s="63" t="s">
         <v>691</v>
       </c>
-      <c r="N203" s="63" t="s">
-        <v>692</v>
-      </c>
       <c r="O203" s="16" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="P203" s="15" t="s">
         <v>71</v>
@@ -23563,7 +23568,7 @@
       <c r="AX203" s="16"/>
       <c r="AY203" s="16"/>
       <c r="AZ203" s="12" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="BA203" s="19" t="s">
         <v>62</v>
@@ -23572,43 +23577,43 @@
     </row>
     <row r="204" spans="1:75" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="12" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B204" s="20" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C204" s="13">
         <v>46185</v>
       </c>
       <c r="D204" s="132" t="s">
+        <v>682</v>
+      </c>
+      <c r="E204" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="E204" s="16" t="s">
-        <v>684</v>
-      </c>
       <c r="F204" s="12" t="s">
+        <v>752</v>
+      </c>
+      <c r="G204" s="84" t="s">
         <v>753</v>
       </c>
-      <c r="G204" s="84" t="s">
-        <v>754</v>
-      </c>
       <c r="H204" s="16" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="J204" s="16" t="s">
         <v>170</v>
       </c>
       <c r="K204" s="79" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="L204" s="72" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="M204" s="40" t="s">
+        <v>698</v>
+      </c>
+      <c r="O204" s="16" t="s">
         <v>699</v>
-      </c>
-      <c r="O204" s="16" t="s">
-        <v>700</v>
       </c>
       <c r="P204" s="15" t="s">
         <v>71</v>
@@ -23623,10 +23628,10 @@
         <v>73</v>
       </c>
       <c r="AJ204" s="12" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AZ204" s="12" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="BA204" s="19" t="s">
         <v>62</v>
@@ -23656,38 +23661,38 @@
     </row>
     <row r="205" spans="1:75" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="12" t="s">
+        <v>759</v>
+      </c>
+      <c r="B205" s="12" t="s">
         <v>760</v>
-      </c>
-      <c r="B205" s="12" t="s">
-        <v>761</v>
       </c>
       <c r="C205" s="13">
         <v>46185</v>
       </c>
       <c r="D205" s="132" t="s">
+        <v>682</v>
+      </c>
+      <c r="E205" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="E205" s="16" t="s">
-        <v>684</v>
-      </c>
       <c r="F205" s="12" t="s">
+        <v>752</v>
+      </c>
+      <c r="G205" s="84" t="s">
         <v>753</v>
       </c>
-      <c r="G205" s="84" t="s">
-        <v>754</v>
-      </c>
       <c r="H205" s="16" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="J205" s="12" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="K205" s="79" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="L205" s="12"/>
       <c r="M205" s="40" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="P205" s="15" t="s">
         <v>71</v>
@@ -23699,7 +23704,7 @@
         <v>171</v>
       </c>
       <c r="Y205" s="12" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="AH205" s="16" t="s">
         <v>174</v>
@@ -23711,7 +23716,7 @@
         <v>175</v>
       </c>
       <c r="AZ205" s="12" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="BA205" s="19" t="s">
         <v>62</v>
@@ -23741,47 +23746,47 @@
     </row>
     <row r="206" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A206" s="12" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B206" s="20" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C206" s="13">
         <v>46185</v>
       </c>
       <c r="D206" s="132" t="s">
+        <v>682</v>
+      </c>
+      <c r="E206" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="E206" s="16" t="s">
-        <v>684</v>
-      </c>
       <c r="F206" s="12" t="s">
+        <v>752</v>
+      </c>
+      <c r="G206" s="145" t="s">
         <v>753</v>
       </c>
-      <c r="G206" s="145" t="s">
-        <v>754</v>
-      </c>
       <c r="H206" s="16" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="I206" s="30" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="J206" s="12" t="s">
+        <v>763</v>
+      </c>
+      <c r="K206" s="79" t="s">
         <v>764</v>
-      </c>
-      <c r="K206" s="79" t="s">
-        <v>765</v>
       </c>
       <c r="L206" s="12"/>
       <c r="M206" s="40" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="N206" s="63" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="O206" s="135" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="P206" s="15" t="s">
         <v>71</v>
@@ -23797,7 +23802,7 @@
         <v>125</v>
       </c>
       <c r="AC206" s="12" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="AH206" s="15" t="s">
         <v>126</v>
@@ -23809,7 +23814,7 @@
         <v>127</v>
       </c>
       <c r="AZ206" s="12" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="BA206" s="19" t="s">
         <v>62</v>
@@ -23818,45 +23823,45 @@
     </row>
     <row r="207" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A207" s="12" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B207" s="20" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C207" s="13">
         <v>46185</v>
       </c>
       <c r="D207" s="132" t="s">
+        <v>682</v>
+      </c>
+      <c r="E207" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="E207" s="16" t="s">
-        <v>684</v>
-      </c>
       <c r="F207" s="12" t="s">
+        <v>752</v>
+      </c>
+      <c r="G207" s="84" t="s">
         <v>753</v>
       </c>
-      <c r="G207" s="84" t="s">
-        <v>754</v>
-      </c>
       <c r="H207" s="16" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="I207" s="52"/>
       <c r="J207" s="16" t="s">
         <v>170</v>
       </c>
       <c r="K207" s="79" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="L207" s="12"/>
       <c r="M207" s="40" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="N207" s="63" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="O207" s="30" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="P207" s="15" t="s">
         <v>71</v>
@@ -23872,7 +23877,7 @@
         <v>125</v>
       </c>
       <c r="AC207" s="12" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="AH207" s="15" t="s">
         <v>126</v>
@@ -23884,7 +23889,7 @@
         <v>127</v>
       </c>
       <c r="AZ207" s="12" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="BA207" s="19" t="s">
         <v>62</v>
@@ -23893,26 +23898,26 @@
     </row>
     <row r="208" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A208" s="12" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B208" s="82"/>
       <c r="C208" s="13">
         <v>46185</v>
       </c>
       <c r="D208" s="132" t="s">
+        <v>682</v>
+      </c>
+      <c r="E208" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="E208" s="16" t="s">
-        <v>684</v>
-      </c>
       <c r="F208" s="12" t="s">
+        <v>752</v>
+      </c>
+      <c r="G208" s="145" t="s">
         <v>753</v>
       </c>
-      <c r="G208" s="145" t="s">
-        <v>754</v>
-      </c>
       <c r="H208" s="16" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="I208" s="16"/>
       <c r="J208" s="16"/>
@@ -23920,7 +23925,7 @@
       <c r="L208" s="16"/>
       <c r="M208" s="16"/>
       <c r="N208" s="16" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="O208" s="16"/>
       <c r="P208" s="3" t="s">
@@ -23931,7 +23936,7 @@
       </c>
       <c r="R208" s="16"/>
       <c r="S208" s="18" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="T208" s="16"/>
       <c r="U208" s="16"/>
@@ -23940,7 +23945,7 @@
         <v>210</v>
       </c>
       <c r="X208" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="Y208" s="16"/>
       <c r="Z208" s="16"/>
@@ -23966,7 +23971,7 @@
       <c r="AP208" s="16"/>
       <c r="AQ208" s="3"/>
       <c r="AR208" s="16" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="AS208" s="16"/>
       <c r="AT208" s="16"/>
@@ -23976,7 +23981,7 @@
       <c r="AX208" s="16"/>
       <c r="AY208" s="16"/>
       <c r="AZ208" s="12" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="BA208" s="19" t="s">
         <v>62</v>
@@ -24006,26 +24011,26 @@
     </row>
     <row r="209" spans="1:75" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A209" s="12" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B209" s="82"/>
       <c r="C209" s="13">
         <v>46185</v>
       </c>
       <c r="D209" s="132" t="s">
+        <v>682</v>
+      </c>
+      <c r="E209" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="E209" s="16" t="s">
-        <v>684</v>
-      </c>
       <c r="F209" s="12" t="s">
+        <v>752</v>
+      </c>
+      <c r="G209" s="145" t="s">
         <v>753</v>
       </c>
-      <c r="G209" s="145" t="s">
-        <v>754</v>
-      </c>
       <c r="H209" s="16" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="I209" s="16"/>
       <c r="J209" s="16"/>
@@ -24049,7 +24054,7 @@
         <v>210</v>
       </c>
       <c r="X209" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="Y209" s="16"/>
       <c r="Z209" s="16"/>
@@ -24075,7 +24080,7 @@
       <c r="AP209" s="16"/>
       <c r="AQ209" s="3"/>
       <c r="AR209" s="16" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="AS209" s="16"/>
       <c r="AT209" s="16"/>
@@ -24085,7 +24090,7 @@
       <c r="AX209" s="16"/>
       <c r="AY209" s="16"/>
       <c r="AZ209" s="12" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="BA209" s="16" t="s">
         <v>62</v>
@@ -24115,44 +24120,44 @@
     </row>
     <row r="210" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A210" s="12" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B210" s="63" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C210" s="13">
         <v>46185</v>
       </c>
       <c r="D210" s="132" t="s">
+        <v>682</v>
+      </c>
+      <c r="E210" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="E210" s="16" t="s">
-        <v>684</v>
-      </c>
       <c r="F210" s="30" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="G210" s="16" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H210" s="16" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="J210" s="16" t="s">
         <v>170</v>
       </c>
       <c r="K210" s="133" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="L210" s="12"/>
       <c r="M210" s="40" t="s">
+        <v>690</v>
+      </c>
+      <c r="N210" s="63" t="s">
         <v>691</v>
       </c>
-      <c r="N210" s="63" t="s">
-        <v>692</v>
-      </c>
       <c r="O210" s="16" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="P210" s="15" t="s">
         <v>71</v>
@@ -24201,7 +24206,7 @@
       <c r="AX210" s="16"/>
       <c r="AY210" s="16"/>
       <c r="AZ210" s="12" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="BA210" s="16" t="s">
         <v>62</v>
@@ -24210,43 +24215,43 @@
     </row>
     <row r="211" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A211" s="12" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B211" s="20" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C211" s="13">
         <v>46185</v>
       </c>
       <c r="D211" s="132" t="s">
+        <v>682</v>
+      </c>
+      <c r="E211" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="E211" s="16" t="s">
-        <v>684</v>
-      </c>
       <c r="F211" s="30" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G211" s="16" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H211" s="16" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="J211" s="16" t="s">
         <v>170</v>
       </c>
       <c r="K211" s="79" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="L211" s="72" t="s">
+        <v>778</v>
+      </c>
+      <c r="M211" s="40" t="s">
+        <v>698</v>
+      </c>
+      <c r="O211" s="16" t="s">
         <v>779</v>
-      </c>
-      <c r="M211" s="40" t="s">
-        <v>699</v>
-      </c>
-      <c r="O211" s="16" t="s">
-        <v>780</v>
       </c>
       <c r="P211" s="15" t="s">
         <v>71</v>
@@ -24261,10 +24266,10 @@
         <v>73</v>
       </c>
       <c r="AJ211" s="12" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AZ211" s="12" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="BA211" s="16" t="s">
         <v>62</v>
@@ -24294,45 +24299,45 @@
     </row>
     <row r="212" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A212" s="12" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B212" s="20" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C212" s="13">
         <v>46185</v>
       </c>
       <c r="D212" s="132" t="s">
+        <v>682</v>
+      </c>
+      <c r="E212" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="E212" s="16" t="s">
-        <v>684</v>
-      </c>
       <c r="F212" s="30" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="G212" s="16" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H212" s="16" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="I212" s="52"/>
       <c r="J212" s="16" t="s">
         <v>170</v>
       </c>
       <c r="K212" s="79" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="L212" s="12"/>
       <c r="M212" s="40" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="N212" s="63" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="O212" s="30" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="P212" s="15" t="s">
         <v>71</v>
@@ -24348,7 +24353,7 @@
         <v>125</v>
       </c>
       <c r="AC212" s="12" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="AH212" s="15" t="s">
         <v>126</v>
@@ -24360,7 +24365,7 @@
         <v>127</v>
       </c>
       <c r="AZ212" s="12" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="BA212" s="16" t="s">
         <v>62</v>
@@ -24369,26 +24374,26 @@
     </row>
     <row r="213" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A213" s="12" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B213" s="82"/>
       <c r="C213" s="13">
         <v>46185</v>
       </c>
       <c r="D213" s="132" t="s">
+        <v>682</v>
+      </c>
+      <c r="E213" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="E213" s="16" t="s">
-        <v>684</v>
-      </c>
       <c r="F213" s="30" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="G213" s="16" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H213" s="16" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="I213" s="16"/>
       <c r="J213" s="16" t="s">
@@ -24398,7 +24403,7 @@
       <c r="L213" s="16"/>
       <c r="M213" s="16"/>
       <c r="N213" s="3" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="O213" s="146"/>
       <c r="P213" s="3" t="s">
@@ -24409,7 +24414,7 @@
       </c>
       <c r="R213" s="16"/>
       <c r="S213" s="18" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="T213" s="16"/>
       <c r="U213" s="16"/>
@@ -24418,7 +24423,7 @@
         <v>210</v>
       </c>
       <c r="X213" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="Y213" s="16"/>
       <c r="Z213" s="16"/>
@@ -24444,7 +24449,7 @@
       <c r="AP213" s="16"/>
       <c r="AQ213" s="3"/>
       <c r="AR213" s="16" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="AS213" s="16"/>
       <c r="AT213" s="16"/>
@@ -24482,26 +24487,26 @@
     </row>
     <row r="214" spans="1:75" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A214" s="12" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B214" s="82"/>
       <c r="C214" s="13">
         <v>46185</v>
       </c>
       <c r="D214" s="132" t="s">
+        <v>682</v>
+      </c>
+      <c r="E214" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="E214" s="16" t="s">
-        <v>684</v>
-      </c>
       <c r="F214" s="30" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="G214" s="16" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H214" s="16" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="I214" s="16"/>
       <c r="J214" s="16" t="s">
@@ -24527,7 +24532,7 @@
         <v>210</v>
       </c>
       <c r="X214" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="Y214" s="16"/>
       <c r="Z214" s="16"/>
@@ -24553,7 +24558,7 @@
       <c r="AP214" s="16"/>
       <c r="AQ214" s="3"/>
       <c r="AR214" s="16" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="AS214" s="16"/>
       <c r="AT214" s="16"/>
@@ -24591,26 +24596,26 @@
     </row>
     <row r="215" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A215" s="12" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B215" s="82"/>
       <c r="C215" s="13">
         <v>46185</v>
       </c>
       <c r="D215" s="132" t="s">
+        <v>682</v>
+      </c>
+      <c r="E215" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="E215" s="16" t="s">
-        <v>684</v>
-      </c>
       <c r="F215" s="30" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="G215" s="16" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H215" s="16" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="I215" s="118"/>
       <c r="J215" s="16" t="s">
@@ -24636,7 +24641,7 @@
         <v>210</v>
       </c>
       <c r="X215" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="Y215" s="118"/>
       <c r="Z215" s="118"/>
@@ -24662,7 +24667,7 @@
       <c r="AP215" s="118"/>
       <c r="AQ215" s="76"/>
       <c r="AR215" s="16" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="AS215" s="118"/>
       <c r="AT215" s="118"/>
@@ -24700,36 +24705,36 @@
     </row>
     <row r="216" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A216" s="19" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B216" s="136" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="C216" s="77">
         <v>46185</v>
       </c>
       <c r="D216" s="132" t="s">
+        <v>682</v>
+      </c>
+      <c r="E216" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="E216" s="16" t="s">
-        <v>684</v>
-      </c>
       <c r="F216" s="12" t="s">
+        <v>791</v>
+      </c>
+      <c r="G216" s="76" t="s">
         <v>792</v>
       </c>
-      <c r="G216" s="76" t="s">
+      <c r="H216" s="3" t="s">
         <v>793</v>
-      </c>
-      <c r="H216" s="3" t="s">
-        <v>794</v>
       </c>
       <c r="I216" s="3"/>
       <c r="J216" s="141"/>
       <c r="K216" s="148" t="s">
+        <v>795</v>
+      </c>
+      <c r="L216" s="3" t="s">
         <v>796</v>
-      </c>
-      <c r="L216" s="3" t="s">
-        <v>797</v>
       </c>
       <c r="M216" s="3"/>
       <c r="N216" s="3"/>
@@ -24748,7 +24753,7 @@
       <c r="W216" s="3"/>
       <c r="X216" s="3"/>
       <c r="Y216" s="3" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="Z216" s="3"/>
       <c r="AA216" s="76"/>
@@ -24763,7 +24768,7 @@
         <v>275</v>
       </c>
       <c r="AJ216" s="3" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="AK216" s="3"/>
       <c r="AL216" s="3"/>
@@ -24781,7 +24786,7 @@
       <c r="AX216" s="3"/>
       <c r="AY216" s="3"/>
       <c r="AZ216" s="12" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="BA216" s="3" t="s">
         <v>62</v>
@@ -24811,49 +24816,49 @@
     </row>
     <row r="217" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A217" s="19" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B217" s="19" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="C217" s="77">
         <v>46185</v>
       </c>
       <c r="D217" s="132" t="s">
+        <v>682</v>
+      </c>
+      <c r="E217" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="E217" s="16" t="s">
-        <v>684</v>
-      </c>
       <c r="F217" s="12" t="s">
+        <v>791</v>
+      </c>
+      <c r="G217" s="76" t="s">
         <v>792</v>
       </c>
-      <c r="G217" s="76" t="s">
+      <c r="H217" s="3" t="s">
         <v>793</v>
       </c>
-      <c r="H217" s="3" t="s">
-        <v>794</v>
-      </c>
       <c r="I217" s="19" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="J217" s="137"/>
       <c r="K217" s="149" t="s">
+        <v>801</v>
+      </c>
+      <c r="L217" s="72" t="s">
         <v>802</v>
-      </c>
-      <c r="L217" s="72" t="s">
-        <v>803</v>
       </c>
       <c r="M217" s="19"/>
       <c r="N217" s="62" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="O217" s="19"/>
       <c r="P217" s="19" t="s">
+        <v>804</v>
+      </c>
+      <c r="Q217" s="137" t="s">
         <v>805</v>
-      </c>
-      <c r="Q217" s="137" t="s">
-        <v>806</v>
       </c>
       <c r="R217" s="19"/>
       <c r="S217" s="19"/>
@@ -24894,7 +24899,7 @@
       <c r="AX217" s="19"/>
       <c r="AY217" s="19"/>
       <c r="AZ217" s="12" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="BA217" s="19" t="s">
         <v>62</v>
@@ -24924,47 +24929,47 @@
     </row>
     <row r="218" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A218" s="76" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B218" s="20" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C218" s="13">
         <v>46185</v>
       </c>
       <c r="D218" s="132" t="s">
+        <v>682</v>
+      </c>
+      <c r="E218" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="E218" s="16" t="s">
-        <v>684</v>
-      </c>
       <c r="F218" s="12" t="s">
+        <v>810</v>
+      </c>
+      <c r="G218" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="H218" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="I218" s="30" t="s">
+        <v>725</v>
+      </c>
+      <c r="J218" s="12" t="s">
         <v>811</v>
       </c>
-      <c r="G218" s="3" t="s">
-        <v>808</v>
-      </c>
-      <c r="H218" s="3" t="s">
-        <v>809</v>
-      </c>
-      <c r="I218" s="30" t="s">
-        <v>726</v>
-      </c>
-      <c r="J218" s="12" t="s">
+      <c r="K218" s="79" t="s">
         <v>812</v>
-      </c>
-      <c r="K218" s="79" t="s">
-        <v>813</v>
       </c>
       <c r="L218" s="12"/>
       <c r="M218" s="40" t="s">
+        <v>813</v>
+      </c>
+      <c r="N218" s="63" t="s">
+        <v>728</v>
+      </c>
+      <c r="O218" s="42" t="s">
         <v>814</v>
-      </c>
-      <c r="N218" s="63" t="s">
-        <v>729</v>
-      </c>
-      <c r="O218" s="42" t="s">
-        <v>815</v>
       </c>
       <c r="P218" s="15" t="s">
         <v>71</v>
@@ -24980,7 +24985,7 @@
         <v>125</v>
       </c>
       <c r="AC218" s="12" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="AH218" s="15" t="s">
         <v>126</v>
@@ -24992,7 +24997,7 @@
         <v>127</v>
       </c>
       <c r="AZ218" s="12" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="BA218" s="16" t="s">
         <v>62</v>
@@ -25001,42 +25006,42 @@
     </row>
     <row r="219" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A219" s="76" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B219" s="136" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C219" s="13">
         <v>46185</v>
       </c>
       <c r="D219" s="132" t="s">
+        <v>682</v>
+      </c>
+      <c r="E219" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="E219" s="16" t="s">
-        <v>684</v>
-      </c>
       <c r="F219" s="12" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="G219" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="H219" s="3" t="s">
         <v>808</v>
       </c>
-      <c r="H219" s="3" t="s">
-        <v>809</v>
-      </c>
       <c r="I219" s="136" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="J219" s="141"/>
       <c r="K219" s="133" t="s">
+        <v>817</v>
+      </c>
+      <c r="L219" s="3" t="s">
         <v>818</v>
-      </c>
-      <c r="L219" s="3" t="s">
-        <v>819</v>
       </c>
       <c r="M219" s="3"/>
       <c r="N219" s="12" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="O219" s="3"/>
       <c r="P219" s="76" t="s">
@@ -25057,10 +25062,10 @@
       </c>
       <c r="Z219" s="3"/>
       <c r="AA219" s="18" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="AB219" s="3" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AC219" s="3" t="s">
         <v>59</v>
@@ -25074,7 +25079,7 @@
         <v>87</v>
       </c>
       <c r="AJ219" s="12" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="AK219" s="3"/>
       <c r="AL219" s="3"/>
@@ -25092,7 +25097,7 @@
       <c r="AX219" s="3"/>
       <c r="AY219" s="3"/>
       <c r="AZ219" s="12" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="BA219" s="16" t="s">
         <v>62</v>
@@ -25122,42 +25127,42 @@
     </row>
     <row r="220" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A220" s="76" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B220" s="136" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C220" s="13">
         <v>46185</v>
       </c>
       <c r="D220" s="132" t="s">
+        <v>682</v>
+      </c>
+      <c r="E220" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="E220" s="16" t="s">
-        <v>684</v>
-      </c>
       <c r="F220" s="12" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="G220" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="H220" s="3" t="s">
         <v>808</v>
       </c>
-      <c r="H220" s="3" t="s">
-        <v>809</v>
-      </c>
       <c r="I220" s="136" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="J220" s="141"/>
       <c r="K220" s="133" t="s">
+        <v>823</v>
+      </c>
+      <c r="L220" s="3" t="s">
         <v>824</v>
-      </c>
-      <c r="L220" s="3" t="s">
-        <v>825</v>
       </c>
       <c r="M220" s="3"/>
       <c r="N220" s="12" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="O220" s="3"/>
       <c r="P220" s="76" t="s">
@@ -25178,10 +25183,10 @@
       </c>
       <c r="Z220" s="3"/>
       <c r="AA220" s="18" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="AB220" s="3" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AC220" s="3" t="s">
         <v>59</v>
@@ -25195,7 +25200,7 @@
         <v>87</v>
       </c>
       <c r="AJ220" s="12" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="AK220" s="3"/>
       <c r="AL220" s="3"/>
@@ -25213,7 +25218,7 @@
       <c r="AX220" s="3"/>
       <c r="AY220" s="3"/>
       <c r="AZ220" s="12" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="BA220" s="16" t="s">
         <v>62</v>
@@ -25243,37 +25248,37 @@
     </row>
     <row r="221" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A221" s="76" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B221" s="15" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C221" s="13">
         <v>46185</v>
       </c>
       <c r="D221" s="132" t="s">
+        <v>682</v>
+      </c>
+      <c r="E221" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="E221" s="16" t="s">
-        <v>684</v>
-      </c>
       <c r="F221" s="12" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="G221" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="H221" s="3" t="s">
         <v>808</v>
-      </c>
-      <c r="H221" s="3" t="s">
-        <v>809</v>
       </c>
       <c r="J221" s="16" t="s">
         <v>170</v>
       </c>
       <c r="K221" s="79" t="s">
+        <v>828</v>
+      </c>
+      <c r="L221" s="18" t="s">
         <v>829</v>
-      </c>
-      <c r="L221" s="18" t="s">
-        <v>830</v>
       </c>
       <c r="N221" s="136" t="s">
         <v>84</v>
@@ -25282,7 +25287,7 @@
         <v>56</v>
       </c>
       <c r="Q221" s="12" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="Y221" s="12" t="s">
         <v>86</v>
@@ -25291,10 +25296,10 @@
         <v>59</v>
       </c>
       <c r="AJ221" s="16" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="AZ221" s="12" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="BA221" s="16" t="s">
         <v>62</v>
@@ -25303,35 +25308,35 @@
     </row>
     <row r="222" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A222" s="76" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B222" s="20" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="C222" s="13">
         <v>46185</v>
       </c>
       <c r="D222" s="132" t="s">
+        <v>682</v>
+      </c>
+      <c r="E222" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="E222" s="16" t="s">
-        <v>684</v>
-      </c>
       <c r="F222" s="12" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="G222" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="H222" s="3" t="s">
         <v>808</v>
-      </c>
-      <c r="H222" s="3" t="s">
-        <v>809</v>
       </c>
       <c r="J222" s="137"/>
       <c r="K222" s="148" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="L222" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="P222" s="15" t="s">
         <v>71</v>
@@ -25340,13 +25345,13 @@
         <v>72</v>
       </c>
       <c r="Y222" s="3" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="AI222" s="31" t="s">
         <v>275</v>
       </c>
       <c r="AZ222" s="12" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="BA222" s="16" t="s">
         <v>62</v>
@@ -25376,49 +25381,49 @@
     </row>
     <row r="223" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A223" s="76" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B223" s="19" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C223" s="77">
         <v>46185</v>
       </c>
       <c r="D223" s="132" t="s">
+        <v>682</v>
+      </c>
+      <c r="E223" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="E223" s="16" t="s">
-        <v>684</v>
-      </c>
       <c r="F223" s="12" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="G223" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="H223" s="3" t="s">
         <v>808</v>
       </c>
-      <c r="H223" s="3" t="s">
-        <v>809</v>
-      </c>
       <c r="I223" s="19" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="J223" s="137"/>
       <c r="K223" s="149" t="s">
+        <v>834</v>
+      </c>
+      <c r="L223" s="72" t="s">
         <v>835</v>
-      </c>
-      <c r="L223" s="72" t="s">
-        <v>836</v>
       </c>
       <c r="M223" s="19"/>
       <c r="N223" s="62" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="O223" s="19"/>
       <c r="P223" s="19" t="s">
+        <v>804</v>
+      </c>
+      <c r="Q223" s="137" t="s">
         <v>805</v>
-      </c>
-      <c r="Q223" s="137" t="s">
-        <v>806</v>
       </c>
       <c r="R223" s="19"/>
       <c r="S223" s="19"/>
@@ -25459,7 +25464,7 @@
       <c r="AX223" s="19"/>
       <c r="AY223" s="19"/>
       <c r="AZ223" s="12" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="BA223" s="16" t="s">
         <v>62</v>
@@ -25489,42 +25494,42 @@
     </row>
     <row r="224" spans="1:75" ht="13" x14ac:dyDescent="0.3">
       <c r="A224" s="19" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B224" s="136" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C224" s="77">
         <v>46195</v>
       </c>
       <c r="D224" s="132" t="s">
+        <v>682</v>
+      </c>
+      <c r="E224" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="E224" s="16" t="s">
-        <v>684</v>
-      </c>
       <c r="F224" s="12" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="G224" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="H224" s="3" t="s">
         <v>808</v>
       </c>
-      <c r="H224" s="3" t="s">
-        <v>809</v>
-      </c>
       <c r="I224" s="136" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="J224" s="3"/>
       <c r="K224" s="133" t="s">
+        <v>841</v>
+      </c>
+      <c r="L224" s="3" t="s">
         <v>842</v>
-      </c>
-      <c r="L224" s="3" t="s">
-        <v>843</v>
       </c>
       <c r="M224" s="3"/>
       <c r="N224" s="12" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="O224" s="3"/>
       <c r="P224" s="76" t="s">
@@ -25545,10 +25550,10 @@
       </c>
       <c r="Z224" s="3"/>
       <c r="AA224" s="3" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="AB224" s="3" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AC224" s="3" t="s">
         <v>59</v>
@@ -25562,7 +25567,7 @@
         <v>87</v>
       </c>
       <c r="AJ224" s="12" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="AK224" s="3"/>
       <c r="AL224" s="3"/>
@@ -25580,7 +25585,7 @@
       <c r="AX224" s="3"/>
       <c r="AY224" s="3"/>
       <c r="AZ224" s="12" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="BA224" s="3" t="s">
         <v>62</v>
@@ -25610,25 +25615,25 @@
     </row>
     <row r="225" spans="1:55" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A225" s="12" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C225" s="13">
         <v>46185</v>
       </c>
       <c r="D225" s="132" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E225" s="16" t="s">
         <v>83</v>
       </c>
       <c r="F225" s="12" t="s">
+        <v>845</v>
+      </c>
+      <c r="G225" s="19" t="s">
         <v>846</v>
       </c>
-      <c r="G225" s="19" t="s">
-        <v>847</v>
-      </c>
       <c r="H225" s="3" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="BA225" s="12" t="s">
         <v>62</v>
@@ -25637,25 +25642,25 @@
     </row>
     <row r="226" spans="1:55" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A226" s="12" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="C226" s="13">
         <v>46185</v>
       </c>
       <c r="D226" s="132" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E226" s="16" t="s">
         <v>83</v>
       </c>
       <c r="F226" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="G226" s="150" t="s">
         <v>849</v>
       </c>
-      <c r="G226" s="150" t="s">
+      <c r="H226" s="76" t="s">
         <v>850</v>
-      </c>
-      <c r="H226" s="76" t="s">
-        <v>851</v>
       </c>
       <c r="BA226" s="12" t="s">
         <v>62</v>
@@ -25664,28 +25669,28 @@
     </row>
     <row r="227" spans="1:55" ht="13" x14ac:dyDescent="0.3">
       <c r="A227" s="12" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B227" s="151" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C227" s="13">
         <v>46185</v>
       </c>
       <c r="D227" s="132" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E227" s="16" t="s">
         <v>83</v>
       </c>
       <c r="F227" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="G227" s="150" t="s">
         <v>849</v>
       </c>
-      <c r="G227" s="150" t="s">
+      <c r="H227" s="76" t="s">
         <v>850</v>
-      </c>
-      <c r="H227" s="76" t="s">
-        <v>851</v>
       </c>
       <c r="K227" s="12"/>
       <c r="L227" s="12"/>
@@ -25693,10 +25698,10 @@
         <v>121</v>
       </c>
       <c r="N227" s="63" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="O227" s="42" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="P227" s="15" t="s">
         <v>71</v>
@@ -25721,7 +25726,7 @@
         <v>127</v>
       </c>
       <c r="AM227" s="19" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="BA227" s="16" t="s">
         <v>62</v>
@@ -25730,40 +25735,40 @@
     </row>
     <row r="228" spans="1:55" ht="13" x14ac:dyDescent="0.3">
       <c r="A228" s="12" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B228" s="12" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C228" s="13">
         <v>46185</v>
       </c>
       <c r="D228" s="132" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E228" s="16" t="s">
         <v>83</v>
       </c>
       <c r="F228" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="G228" s="150" t="s">
         <v>849</v>
       </c>
-      <c r="G228" s="150" t="s">
+      <c r="H228" s="76" t="s">
         <v>850</v>
       </c>
-      <c r="H228" s="76" t="s">
-        <v>851</v>
-      </c>
       <c r="I228" s="19" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="N228" s="62" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="P228" s="19" t="s">
+        <v>804</v>
+      </c>
+      <c r="Q228" s="137" t="s">
         <v>805</v>
-      </c>
-      <c r="Q228" s="137" t="s">
-        <v>806</v>
       </c>
       <c r="Y228" s="12" t="s">
         <v>211</v>
@@ -25778,25 +25783,25 @@
     </row>
     <row r="229" spans="1:55" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A229" s="12" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="C229" s="13">
         <v>46185</v>
       </c>
       <c r="D229" s="132" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E229" s="16" t="s">
         <v>83</v>
       </c>
       <c r="F229" s="19" t="s">
+        <v>857</v>
+      </c>
+      <c r="G229" s="19" t="s">
         <v>858</v>
       </c>
-      <c r="G229" s="19" t="s">
-        <v>859</v>
-      </c>
       <c r="H229" s="76" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="BA229" s="12" t="s">
         <v>62</v>
@@ -25805,32 +25810,32 @@
     </row>
     <row r="230" spans="1:55" ht="13" x14ac:dyDescent="0.3">
       <c r="A230" s="12" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B230" s="152" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="C230" s="13">
         <v>46217</v>
       </c>
       <c r="D230" s="132" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E230" s="16" t="s">
         <v>83</v>
       </c>
       <c r="F230" s="19" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="G230" s="100" t="s">
+        <v>859</v>
+      </c>
+      <c r="H230" s="115" t="s">
         <v>860</v>
-      </c>
-      <c r="H230" s="115" t="s">
-        <v>861</v>
       </c>
       <c r="K230" s="12"/>
       <c r="L230" s="4" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="M230" s="19"/>
       <c r="P230" s="15" t="s">
@@ -25849,22 +25854,22 @@
     </row>
     <row r="231" spans="1:55" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A231" s="12" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C231" s="65">
         <v>46281</v>
       </c>
       <c r="D231" s="16" t="s">
+        <v>863</v>
+      </c>
+      <c r="E231" s="30" t="s">
         <v>864</v>
       </c>
-      <c r="E231" s="30" t="s">
+      <c r="F231" s="30" t="s">
         <v>865</v>
       </c>
-      <c r="F231" s="30" t="s">
+      <c r="H231" s="52" t="s">
         <v>866</v>
-      </c>
-      <c r="H231" s="52" t="s">
-        <v>867</v>
       </c>
       <c r="BC231" s="19"/>
     </row>
@@ -29167,6 +29172,7 @@
       <c r="BC1055" s="19"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="54" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="M3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="M9" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
